--- a/research/traditional_assets/database/data/jordan/jordan_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_oilfield_svcs_equip.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1187934524855038</v>
+        <v>0.1185918655805328</v>
       </c>
       <c r="C2">
-        <v>1979.0902837508</v>
+        <v>1966.166417738222</v>
       </c>
       <c r="D2">
-        <v>1954.2902837508</v>
+        <v>1959.702417738222</v>
       </c>
       <c r="E2">
-        <v>-1128.8</v>
+        <v>-1110.464</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18.336</v>
       </c>
       <c r="G2">
         <v>24.8</v>
@@ -1451,28 +1451,28 @@
         <v>220.948</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9223007999999999</v>
       </c>
       <c r="N2">
-        <v>220.948</v>
+        <v>220.0256992</v>
       </c>
       <c r="O2">
-        <v>44.18960000000001</v>
+        <v>44.00513984000001</v>
       </c>
       <c r="P2">
-        <v>176.7584</v>
+        <v>176.02055936</v>
       </c>
       <c r="Q2">
-        <v>176.9354</v>
+        <v>176.19755936</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1187934524855038</v>
+        <v>0.1193832985661947</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8057672793224576</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>239.5617568585</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1185918655805328</v>
+        <v>0.1183902786755618</v>
       </c>
       <c r="C3">
-        <v>1966.166417738222</v>
+        <v>1953.272611269696</v>
       </c>
       <c r="D3">
-        <v>1959.702417738222</v>
+        <v>1965.144611269696</v>
       </c>
       <c r="E3">
-        <v>-1110.464</v>
+        <v>-1092.128</v>
       </c>
       <c r="F3">
-        <v>18.336</v>
+        <v>36.672</v>
       </c>
       <c r="G3">
         <v>24.8</v>
@@ -1533,28 +1533,28 @@
         <v>220.948</v>
       </c>
       <c r="M3">
-        <v>0.9223007999999999</v>
+        <v>1.8446016</v>
       </c>
       <c r="N3">
-        <v>220.0256992</v>
+        <v>219.1033984</v>
       </c>
       <c r="O3">
-        <v>44.00513984000001</v>
+        <v>43.82067968</v>
       </c>
       <c r="P3">
-        <v>176.02055936</v>
+        <v>175.28271872</v>
       </c>
       <c r="Q3">
-        <v>176.19755936</v>
+        <v>175.45971872</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1193832985661947</v>
+        <v>0.1199851823220018</v>
       </c>
       <c r="T3">
-        <v>0.8057672793224576</v>
+        <v>0.8123581531462067</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>239.5617568585</v>
+        <v>119.78087842925</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1183902786755618</v>
+        <v>0.1181886917705908</v>
       </c>
       <c r="C4">
-        <v>1953.272611269696</v>
+        <v>1940.409115473277</v>
       </c>
       <c r="D4">
-        <v>1965.144611269696</v>
+        <v>1970.617115473277</v>
       </c>
       <c r="E4">
-        <v>-1092.128</v>
+        <v>-1073.792</v>
       </c>
       <c r="F4">
-        <v>36.672</v>
+        <v>55.008</v>
       </c>
       <c r="G4">
         <v>24.8</v>
@@ -1615,28 +1615,28 @@
         <v>220.948</v>
       </c>
       <c r="M4">
-        <v>1.8446016</v>
+        <v>2.7669024</v>
       </c>
       <c r="N4">
-        <v>219.1033984</v>
+        <v>218.1810976</v>
       </c>
       <c r="O4">
-        <v>43.82067968</v>
+        <v>43.63621952</v>
       </c>
       <c r="P4">
-        <v>175.28271872</v>
+        <v>174.54487808</v>
       </c>
       <c r="Q4">
-        <v>175.45971872</v>
+        <v>174.72187808</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1199851823220018</v>
+        <v>0.1205994760521554</v>
       </c>
       <c r="T4">
-        <v>0.8123581531462067</v>
+        <v>0.8190849212756002</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>119.78087842925</v>
+        <v>79.85391895283333</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1181886917705908</v>
+        <v>0.1179871048656198</v>
       </c>
       <c r="C5">
-        <v>1940.409115473277</v>
+        <v>1927.576184282182</v>
       </c>
       <c r="D5">
-        <v>1970.617115473277</v>
+        <v>1976.120184282182</v>
       </c>
       <c r="E5">
-        <v>-1073.792</v>
+        <v>-1055.456</v>
       </c>
       <c r="F5">
-        <v>55.008</v>
+        <v>73.34399999999999</v>
       </c>
       <c r="G5">
         <v>24.8</v>
@@ -1697,28 +1697,28 @@
         <v>220.948</v>
       </c>
       <c r="M5">
-        <v>2.7669024</v>
+        <v>3.6892032</v>
       </c>
       <c r="N5">
-        <v>218.1810976</v>
+        <v>217.2587968</v>
       </c>
       <c r="O5">
-        <v>43.63621952</v>
+        <v>43.45175936</v>
       </c>
       <c r="P5">
-        <v>174.54487808</v>
+        <v>173.80703744</v>
       </c>
       <c r="Q5">
-        <v>174.72187808</v>
+        <v>173.98403744</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1205994760521554</v>
+        <v>0.1212265675683539</v>
       </c>
       <c r="T5">
-        <v>0.8190849212756002</v>
+        <v>0.8259518304076895</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>79.85391895283333</v>
+        <v>59.890439214625</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1179871048656198</v>
+        <v>0.1177855179606487</v>
       </c>
       <c r="C6">
-        <v>1927.576184282182</v>
+        <v>1914.774074474068</v>
       </c>
       <c r="D6">
-        <v>1976.120184282182</v>
+        <v>1981.654074474068</v>
       </c>
       <c r="E6">
-        <v>-1055.456</v>
+        <v>-1037.12</v>
       </c>
       <c r="F6">
-        <v>73.34399999999999</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="G6">
         <v>24.8</v>
@@ -1779,28 +1779,28 @@
         <v>220.948</v>
       </c>
       <c r="M6">
-        <v>3.6892032</v>
+        <v>4.611504</v>
       </c>
       <c r="N6">
-        <v>217.2587968</v>
+        <v>216.336496</v>
       </c>
       <c r="O6">
-        <v>43.45175936</v>
+        <v>43.2672992</v>
       </c>
       <c r="P6">
-        <v>173.80703744</v>
+        <v>173.0691968</v>
       </c>
       <c r="Q6">
-        <v>173.98403744</v>
+        <v>173.2461968</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1212265675683539</v>
+        <v>0.1218668610112092</v>
       </c>
       <c r="T6">
-        <v>0.8259518304076895</v>
+        <v>0.8329633060478225</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>59.890439214625</v>
+        <v>47.91235137169999</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1177855179606487</v>
+        <v>0.1175839310556777</v>
       </c>
       <c r="C7">
-        <v>1914.774074474068</v>
+        <v>1902.003045710966</v>
       </c>
       <c r="D7">
-        <v>1981.654074474068</v>
+        <v>1987.219045710967</v>
       </c>
       <c r="E7">
-        <v>-1037.12</v>
+        <v>-1018.784</v>
       </c>
       <c r="F7">
-        <v>91.68000000000001</v>
+        <v>110.016</v>
       </c>
       <c r="G7">
         <v>24.8</v>
@@ -1861,28 +1861,28 @@
         <v>220.948</v>
       </c>
       <c r="M7">
-        <v>4.611504</v>
+        <v>5.5338048</v>
       </c>
       <c r="N7">
-        <v>216.336496</v>
+        <v>215.4141952</v>
       </c>
       <c r="O7">
-        <v>43.2672992</v>
+        <v>43.08283904</v>
       </c>
       <c r="P7">
-        <v>173.0691968</v>
+        <v>172.33135616</v>
       </c>
       <c r="Q7">
-        <v>173.2461968</v>
+        <v>172.50835616</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1218668610112092</v>
+        <v>0.1225207777188061</v>
       </c>
       <c r="T7">
-        <v>0.8329633060478225</v>
+        <v>0.8401239620207247</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>47.91235137169999</v>
+        <v>39.92695947641666</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1175839310556777</v>
+        <v>0.1173823441507067</v>
       </c>
       <c r="C8">
-        <v>1902.003045710966</v>
+        <v>1889.263360579909</v>
       </c>
       <c r="D8">
-        <v>1987.219045710967</v>
+        <v>1992.815360579909</v>
       </c>
       <c r="E8">
-        <v>-1018.784</v>
+        <v>-1000.448</v>
       </c>
       <c r="F8">
-        <v>110.016</v>
+        <v>128.352</v>
       </c>
       <c r="G8">
         <v>24.8</v>
@@ -1943,28 +1943,28 @@
         <v>220.948</v>
       </c>
       <c r="M8">
-        <v>5.5338048</v>
+        <v>6.456105599999998</v>
       </c>
       <c r="N8">
-        <v>215.4141952</v>
+        <v>214.4918944</v>
       </c>
       <c r="O8">
-        <v>43.08283904</v>
+        <v>42.89837888</v>
       </c>
       <c r="P8">
-        <v>172.33135616</v>
+        <v>171.59351552</v>
       </c>
       <c r="Q8">
-        <v>172.50835616</v>
+        <v>171.77051552</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1225207777188061</v>
+        <v>0.1231887571512976</v>
       </c>
       <c r="T8">
-        <v>0.8401239620207247</v>
+        <v>0.8474386105951944</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.92695947641666</v>
+        <v>34.22310812264286</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1173823441507067</v>
+        <v>0.1171807572457357</v>
       </c>
       <c r="C9">
-        <v>1889.263360579909</v>
+        <v>1876.555284634216</v>
       </c>
       <c r="D9">
-        <v>1992.815360579909</v>
+        <v>1998.443284634216</v>
       </c>
       <c r="E9">
-        <v>-1000.448</v>
+        <v>-982.112</v>
       </c>
       <c r="F9">
-        <v>128.352</v>
+        <v>146.688</v>
       </c>
       <c r="G9">
         <v>24.8</v>
@@ -2025,28 +2025,28 @@
         <v>220.948</v>
       </c>
       <c r="M9">
-        <v>6.4561056</v>
+        <v>7.378406399999999</v>
       </c>
       <c r="N9">
-        <v>214.4918944</v>
+        <v>213.5695936</v>
       </c>
       <c r="O9">
-        <v>42.89837888</v>
+        <v>42.71391872000001</v>
       </c>
       <c r="P9">
-        <v>171.59351552</v>
+        <v>170.85567488</v>
       </c>
       <c r="Q9">
-        <v>171.77051552</v>
+        <v>171.03267488</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1231887571512976</v>
+        <v>0.1238712578757997</v>
       </c>
       <c r="T9">
-        <v>0.8474386105951944</v>
+        <v>0.8549122732691091</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.22310812264286</v>
+        <v>29.9452196073125</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1171807572457357</v>
+        <v>0.1169791703407647</v>
       </c>
       <c r="C10">
-        <v>1876.555284634216</v>
+        <v>1863.879086435514</v>
       </c>
       <c r="D10">
-        <v>1998.443284634216</v>
+        <v>2004.103086435514</v>
       </c>
       <c r="E10">
-        <v>-982.112</v>
+        <v>-963.776</v>
       </c>
       <c r="F10">
-        <v>146.688</v>
+        <v>165.024</v>
       </c>
       <c r="G10">
         <v>24.8</v>
@@ -2107,28 +2107,28 @@
         <v>220.948</v>
       </c>
       <c r="M10">
-        <v>7.378406399999999</v>
+        <v>8.300707199999998</v>
       </c>
       <c r="N10">
-        <v>213.5695936</v>
+        <v>212.6472928</v>
       </c>
       <c r="O10">
-        <v>42.71391872000001</v>
+        <v>42.52945856</v>
       </c>
       <c r="P10">
-        <v>170.85567488</v>
+        <v>170.11783424</v>
       </c>
       <c r="Q10">
-        <v>171.03267488</v>
+        <v>170.29483424</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1238712578757997</v>
+        <v>0.124568758616225</v>
       </c>
       <c r="T10">
-        <v>0.8549122732691091</v>
+        <v>0.8625501922655274</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.9452196073125</v>
+        <v>26.61797298427778</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1169791703407647</v>
+        <v>0.1167775834357937</v>
       </c>
       <c r="C11">
-        <v>1863.879086435514</v>
+        <v>1851.235037596444</v>
       </c>
       <c r="D11">
-        <v>2004.103086435514</v>
+        <v>2009.795037596444</v>
       </c>
       <c r="E11">
-        <v>-963.776</v>
+        <v>-945.4399999999999</v>
       </c>
       <c r="F11">
-        <v>165.024</v>
+        <v>183.36</v>
       </c>
       <c r="G11">
         <v>24.8</v>
@@ -2189,28 +2189,28 @@
         <v>220.948</v>
       </c>
       <c r="M11">
-        <v>8.300707199999998</v>
+        <v>9.223007999999998</v>
       </c>
       <c r="N11">
-        <v>212.6472928</v>
+        <v>211.724992</v>
       </c>
       <c r="O11">
-        <v>42.52945856</v>
+        <v>42.34499840000001</v>
       </c>
       <c r="P11">
-        <v>170.11783424</v>
+        <v>169.3799936</v>
       </c>
       <c r="Q11">
-        <v>170.29483424</v>
+        <v>169.5569936</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.124568758616225</v>
+        <v>0.1252817593731041</v>
       </c>
       <c r="T11">
-        <v>0.8625501922655274</v>
+        <v>0.8703578427951996</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.61797298427778</v>
+        <v>23.95617568585</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1167775834357937</v>
+        <v>0.1165759965308227</v>
       </c>
       <c r="C12">
-        <v>1851.235037596444</v>
+        <v>1838.62341282412</v>
       </c>
       <c r="D12">
-        <v>2009.795037596444</v>
+        <v>2015.51941282412</v>
       </c>
       <c r="E12">
-        <v>-945.4399999999999</v>
+        <v>-927.1039999999999</v>
       </c>
       <c r="F12">
-        <v>183.36</v>
+        <v>201.696</v>
       </c>
       <c r="G12">
         <v>24.8</v>
@@ -2271,28 +2271,28 @@
         <v>220.948</v>
       </c>
       <c r="M12">
-        <v>9.223008</v>
+        <v>10.1453088</v>
       </c>
       <c r="N12">
-        <v>211.724992</v>
+        <v>210.8026912</v>
       </c>
       <c r="O12">
-        <v>42.34499840000001</v>
+        <v>42.16053824</v>
       </c>
       <c r="P12">
-        <v>169.3799936</v>
+        <v>168.64215296</v>
       </c>
       <c r="Q12">
-        <v>169.5569936</v>
+        <v>168.81915296</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1252817593731041</v>
+        <v>0.1260107826189019</v>
       </c>
       <c r="T12">
-        <v>0.8703578427951998</v>
+        <v>0.8783409461457632</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.95617568585</v>
+        <v>21.77834153259091</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1165759965308227</v>
+        <v>0.1163744096258517</v>
       </c>
       <c r="C13">
-        <v>1838.62341282412</v>
+        <v>1826.044489964322</v>
       </c>
       <c r="D13">
-        <v>2015.51941282412</v>
+        <v>2021.276489964322</v>
       </c>
       <c r="E13">
-        <v>-927.1039999999999</v>
+        <v>-908.768</v>
       </c>
       <c r="F13">
-        <v>201.696</v>
+        <v>220.032</v>
       </c>
       <c r="G13">
         <v>24.8</v>
@@ -2353,28 +2353,28 @@
         <v>220.948</v>
       </c>
       <c r="M13">
-        <v>10.1453088</v>
+        <v>11.0676096</v>
       </c>
       <c r="N13">
-        <v>210.8026912</v>
+        <v>209.8803904</v>
       </c>
       <c r="O13">
-        <v>42.16053824</v>
+        <v>41.97607808000001</v>
       </c>
       <c r="P13">
-        <v>168.64215296</v>
+        <v>167.90431232</v>
       </c>
       <c r="Q13">
-        <v>168.81915296</v>
+        <v>168.08131232</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1260107826189019</v>
+        <v>0.1267563745748315</v>
       </c>
       <c r="T13">
-        <v>0.8783409461457632</v>
+        <v>0.8865054836633852</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.77834153259091</v>
+        <v>19.96347973820833</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1163744096258517</v>
+        <v>0.1161728227208807</v>
       </c>
       <c r="C14">
-        <v>1826.044489964322</v>
+        <v>1813.498550046445</v>
       </c>
       <c r="D14">
-        <v>2021.276489964322</v>
+        <v>2027.066550046445</v>
       </c>
       <c r="E14">
-        <v>-908.768</v>
+        <v>-890.432</v>
       </c>
       <c r="F14">
-        <v>220.032</v>
+        <v>238.368</v>
       </c>
       <c r="G14">
         <v>24.8</v>
@@ -2435,28 +2435,28 @@
         <v>220.948</v>
       </c>
       <c r="M14">
-        <v>11.0676096</v>
+        <v>11.9899104</v>
       </c>
       <c r="N14">
-        <v>209.8803904</v>
+        <v>208.9580896</v>
       </c>
       <c r="O14">
-        <v>41.97607808000001</v>
+        <v>41.79161792</v>
       </c>
       <c r="P14">
-        <v>167.90431232</v>
+        <v>167.16647168</v>
       </c>
       <c r="Q14">
-        <v>168.08131232</v>
+        <v>167.34347168</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1267563745748315</v>
+        <v>0.1275191065757249</v>
       </c>
       <c r="T14">
-        <v>0.8865054836633852</v>
+        <v>0.8948577116986535</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.96347973820833</v>
+        <v>18.42782745065384</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1161728227208807</v>
+        <v>0.1159712358159097</v>
       </c>
       <c r="C15">
-        <v>1813.498550046445</v>
+        <v>1800.985877329239</v>
       </c>
       <c r="D15">
-        <v>2027.066550046445</v>
+        <v>2032.889877329239</v>
       </c>
       <c r="E15">
-        <v>-890.432</v>
+        <v>-872.096</v>
       </c>
       <c r="F15">
-        <v>238.368</v>
+        <v>256.704</v>
       </c>
       <c r="G15">
         <v>24.8</v>
@@ -2517,28 +2517,28 @@
         <v>220.948</v>
       </c>
       <c r="M15">
-        <v>11.9899104</v>
+        <v>12.9122112</v>
       </c>
       <c r="N15">
-        <v>208.9580896</v>
+        <v>208.0357888</v>
       </c>
       <c r="O15">
-        <v>41.79161792</v>
+        <v>41.60715776000001</v>
       </c>
       <c r="P15">
-        <v>167.16647168</v>
+        <v>166.42863104</v>
       </c>
       <c r="Q15">
-        <v>167.34347168</v>
+        <v>166.60563104</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1275191065757249</v>
+        <v>0.1282995765301276</v>
       </c>
       <c r="T15">
-        <v>0.8948577116986535</v>
+        <v>0.9034041775952073</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.42782745065384</v>
+        <v>17.11155406132143</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1159712358159097</v>
+        <v>0.1157696489109387</v>
       </c>
       <c r="C16">
-        <v>1800.985877329239</v>
+        <v>1788.506759347317</v>
       </c>
       <c r="D16">
-        <v>2032.889877329239</v>
+        <v>2038.746759347317</v>
       </c>
       <c r="E16">
-        <v>-872.096</v>
+        <v>-853.76</v>
       </c>
       <c r="F16">
-        <v>256.704</v>
+        <v>275.04</v>
       </c>
       <c r="G16">
         <v>24.8</v>
@@ -2599,28 +2599,28 @@
         <v>220.948</v>
       </c>
       <c r="M16">
-        <v>12.9122112</v>
+        <v>13.834512</v>
       </c>
       <c r="N16">
-        <v>208.0357888</v>
+        <v>207.113488</v>
       </c>
       <c r="O16">
-        <v>41.60715776000001</v>
+        <v>41.42269760000001</v>
       </c>
       <c r="P16">
-        <v>166.42863104</v>
+        <v>165.6907904</v>
       </c>
       <c r="Q16">
-        <v>166.60563104</v>
+        <v>165.8677904</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1282995765301276</v>
+        <v>0.1290984104834573</v>
       </c>
       <c r="T16">
-        <v>0.9034041775952073</v>
+        <v>0.9121517368069739</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.11155406132143</v>
+        <v>15.97078379056667</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1157696489109387</v>
+        <v>0.1155680620059676</v>
       </c>
       <c r="C17">
-        <v>1788.506759347317</v>
+        <v>1776.06148695849</v>
       </c>
       <c r="D17">
-        <v>2038.746759347317</v>
+        <v>2044.63748695849</v>
       </c>
       <c r="E17">
-        <v>-853.76</v>
+        <v>-835.424</v>
       </c>
       <c r="F17">
-        <v>275.04</v>
+        <v>293.376</v>
       </c>
       <c r="G17">
         <v>24.8</v>
@@ -2681,28 +2681,28 @@
         <v>220.948</v>
       </c>
       <c r="M17">
-        <v>13.834512</v>
+        <v>14.7568128</v>
       </c>
       <c r="N17">
-        <v>207.113488</v>
+        <v>206.1911872</v>
       </c>
       <c r="O17">
-        <v>41.42269760000001</v>
+        <v>41.23823744000001</v>
       </c>
       <c r="P17">
-        <v>165.6907904</v>
+        <v>164.95294976</v>
       </c>
       <c r="Q17">
-        <v>165.8677904</v>
+        <v>165.12994976</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1290984104834573</v>
+        <v>0.1299162642928186</v>
       </c>
       <c r="T17">
-        <v>0.9121517368069739</v>
+        <v>0.9211075712380683</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.97078379056667</v>
+        <v>14.97260980365625</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1155680620059676</v>
+        <v>0.1153664751009967</v>
       </c>
       <c r="C18">
-        <v>1776.06148695849</v>
+        <v>1763.650354391908</v>
       </c>
       <c r="D18">
-        <v>2044.63748695849</v>
+        <v>2050.562354391908</v>
       </c>
       <c r="E18">
-        <v>-835.424</v>
+        <v>-817.088</v>
       </c>
       <c r="F18">
-        <v>293.376</v>
+        <v>311.712</v>
       </c>
       <c r="G18">
         <v>24.8</v>
@@ -2763,28 +2763,28 @@
         <v>220.948</v>
       </c>
       <c r="M18">
-        <v>14.7568128</v>
+        <v>15.6791136</v>
       </c>
       <c r="N18">
-        <v>206.1911872</v>
+        <v>205.2688864</v>
       </c>
       <c r="O18">
-        <v>41.23823744000001</v>
+        <v>41.05377728000001</v>
       </c>
       <c r="P18">
-        <v>164.95294976</v>
+        <v>164.21510912</v>
       </c>
       <c r="Q18">
-        <v>165.12994976</v>
+        <v>164.39210912</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1299162642928186</v>
+        <v>0.1307538254228875</v>
       </c>
       <c r="T18">
-        <v>0.9211075712380683</v>
+        <v>0.9302792089084664</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.97260980365625</v>
+        <v>14.0918680505</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1153664751009967</v>
+        <v>0.1151648881960257</v>
       </c>
       <c r="C19">
-        <v>1763.650354391908</v>
+        <v>1751.27365929706</v>
       </c>
       <c r="D19">
-        <v>2050.562354391908</v>
+        <v>2056.52165929706</v>
       </c>
       <c r="E19">
-        <v>-817.088</v>
+        <v>-798.752</v>
       </c>
       <c r="F19">
-        <v>311.712</v>
+        <v>330.048</v>
       </c>
       <c r="G19">
         <v>24.8</v>
@@ -2845,28 +2845,28 @@
         <v>220.948</v>
       </c>
       <c r="M19">
-        <v>15.6791136</v>
+        <v>16.6014144</v>
       </c>
       <c r="N19">
-        <v>205.2688864</v>
+        <v>204.3465856</v>
       </c>
       <c r="O19">
-        <v>41.05377728000001</v>
+        <v>40.86931712000001</v>
       </c>
       <c r="P19">
-        <v>164.21510912</v>
+        <v>163.47726848</v>
       </c>
       <c r="Q19">
-        <v>164.39210912</v>
+        <v>163.65426848</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1307538254228875</v>
+        <v>0.131611814873202</v>
       </c>
       <c r="T19">
-        <v>0.9302792089084664</v>
+        <v>0.9396745450586302</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.0918680505</v>
+        <v>13.30898649213889</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1151648881960257</v>
+        <v>0.1151913012910546</v>
       </c>
       <c r="C20">
-        <v>1751.27365929706</v>
+        <v>1732.154865185903</v>
       </c>
       <c r="D20">
-        <v>2056.52165929706</v>
+        <v>2055.738865185903</v>
       </c>
       <c r="E20">
-        <v>-798.752</v>
+        <v>-780.4159999999999</v>
       </c>
       <c r="F20">
-        <v>330.0479999999999</v>
+        <v>348.384</v>
       </c>
       <c r="G20">
         <v>24.8</v>
@@ -2927,45 +2927,45 @@
         <v>220.948</v>
       </c>
       <c r="M20">
-        <v>16.6014144</v>
+        <v>18.0462912</v>
       </c>
       <c r="N20">
-        <v>204.3465856</v>
+        <v>202.9017088</v>
       </c>
       <c r="O20">
-        <v>40.86931712000001</v>
+        <v>40.58034176</v>
       </c>
       <c r="P20">
-        <v>163.47726848</v>
+        <v>162.32136704</v>
       </c>
       <c r="Q20">
-        <v>163.65426848</v>
+        <v>162.49836704</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.131611814873202</v>
+        <v>0.1324909892482156</v>
       </c>
       <c r="T20">
-        <v>0.9396745450586301</v>
+        <v>0.9493018648174401</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.30898649213889</v>
+        <v>12.24340212353439</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1151913012910546</v>
+        <v>0.1150017143860836</v>
       </c>
       <c r="C21">
-        <v>1732.154865185903</v>
+        <v>1719.450823473884</v>
       </c>
       <c r="D21">
-        <v>2055.738865185903</v>
+        <v>2061.370823473884</v>
       </c>
       <c r="E21">
-        <v>-780.4159999999999</v>
+        <v>-762.0799999999999</v>
       </c>
       <c r="F21">
-        <v>348.384</v>
+        <v>366.72</v>
       </c>
       <c r="G21">
         <v>24.8</v>
@@ -3009,28 +3009,28 @@
         <v>220.948</v>
       </c>
       <c r="M21">
-        <v>18.0462912</v>
+        <v>18.996096</v>
       </c>
       <c r="N21">
-        <v>202.9017088</v>
+        <v>201.951904</v>
       </c>
       <c r="O21">
-        <v>40.58034176</v>
+        <v>40.3903808</v>
       </c>
       <c r="P21">
-        <v>162.32136704</v>
+        <v>161.5615232</v>
       </c>
       <c r="Q21">
-        <v>162.49836704</v>
+        <v>161.7385232</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1324909892482156</v>
+        <v>0.1333921429826045</v>
       </c>
       <c r="T21">
-        <v>0.9493018648174401</v>
+        <v>0.9591698675702199</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.24340212353439</v>
+        <v>11.63123201735767</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1150017143860836</v>
+        <v>0.1148121274811126</v>
       </c>
       <c r="C22">
-        <v>1719.450823473884</v>
+        <v>1706.777725469289</v>
       </c>
       <c r="D22">
-        <v>2061.370823473884</v>
+        <v>2067.033725469289</v>
       </c>
       <c r="E22">
-        <v>-762.0799999999999</v>
+        <v>-743.7439999999999</v>
       </c>
       <c r="F22">
-        <v>366.72</v>
+        <v>385.056</v>
       </c>
       <c r="G22">
         <v>24.8</v>
@@ -3091,28 +3091,28 @@
         <v>220.948</v>
       </c>
       <c r="M22">
-        <v>18.996096</v>
+        <v>19.9459008</v>
       </c>
       <c r="N22">
-        <v>201.951904</v>
+        <v>201.0020992</v>
       </c>
       <c r="O22">
-        <v>40.3903808</v>
+        <v>40.20041984</v>
       </c>
       <c r="P22">
-        <v>161.5615232</v>
+        <v>160.80167936</v>
       </c>
       <c r="Q22">
-        <v>161.7385232</v>
+        <v>160.97867936</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1333921429826045</v>
+        <v>0.1343161107355856</v>
       </c>
       <c r="T22">
-        <v>0.9591698675702199</v>
+        <v>0.9692876931775009</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.63123201735767</v>
+        <v>11.07736382605493</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1148121274811126</v>
+        <v>0.1146225405761416</v>
       </c>
       <c r="C23">
-        <v>1706.777725469289</v>
+        <v>1694.13582689597</v>
       </c>
       <c r="D23">
-        <v>2067.033725469289</v>
+        <v>2072.72782689597</v>
       </c>
       <c r="E23">
-        <v>-743.7439999999999</v>
+        <v>-725.4079999999999</v>
       </c>
       <c r="F23">
-        <v>385.056</v>
+        <v>403.392</v>
       </c>
       <c r="G23">
         <v>24.8</v>
@@ -3173,28 +3173,28 @@
         <v>220.948</v>
       </c>
       <c r="M23">
-        <v>19.9459008</v>
+        <v>20.8957056</v>
       </c>
       <c r="N23">
-        <v>201.0020992</v>
+        <v>200.0522944</v>
       </c>
       <c r="O23">
-        <v>40.20041984</v>
+        <v>40.01045888</v>
       </c>
       <c r="P23">
-        <v>160.80167936</v>
+        <v>160.04183552</v>
       </c>
       <c r="Q23">
-        <v>160.97867936</v>
+        <v>160.21883552</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1343161107355856</v>
+        <v>0.1352637699694123</v>
       </c>
       <c r="T23">
-        <v>0.9692876931775009</v>
+        <v>0.9796649502106094</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.07736382605493</v>
+        <v>10.57384728850697</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1146225405761416</v>
+        <v>0.1144329536711706</v>
       </c>
       <c r="C24">
-        <v>1694.13582689597</v>
+        <v>1681.525386303354</v>
       </c>
       <c r="D24">
-        <v>2072.72782689597</v>
+        <v>2078.453386303354</v>
       </c>
       <c r="E24">
-        <v>-725.4079999999999</v>
+        <v>-707.0719999999999</v>
       </c>
       <c r="F24">
-        <v>403.392</v>
+        <v>421.728</v>
       </c>
       <c r="G24">
         <v>24.8</v>
@@ -3255,28 +3255,28 @@
         <v>220.948</v>
       </c>
       <c r="M24">
-        <v>20.8957056</v>
+        <v>21.8455104</v>
       </c>
       <c r="N24">
-        <v>200.0522944</v>
+        <v>199.1024896</v>
       </c>
       <c r="O24">
-        <v>40.01045888</v>
+        <v>39.82049792000001</v>
       </c>
       <c r="P24">
-        <v>160.04183552</v>
+        <v>159.28199168</v>
       </c>
       <c r="Q24">
-        <v>160.21883552</v>
+        <v>159.45899168</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1352637699694123</v>
+        <v>0.136236043728793</v>
       </c>
       <c r="T24">
-        <v>0.9796649502106094</v>
+        <v>0.990311746387435</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.57384728850697</v>
+        <v>10.11411479770232</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1144329536711706</v>
+        <v>0.1145697667661996</v>
       </c>
       <c r="C25">
-        <v>1681.525386303354</v>
+        <v>1659.054434942817</v>
       </c>
       <c r="D25">
-        <v>2078.453386303354</v>
+        <v>2074.318434942817</v>
       </c>
       <c r="E25">
-        <v>-707.0719999999999</v>
+        <v>-688.7359999999999</v>
       </c>
       <c r="F25">
-        <v>421.728</v>
+        <v>440.064</v>
       </c>
       <c r="G25">
         <v>24.8</v>
@@ -3337,45 +3337,45 @@
         <v>220.948</v>
       </c>
       <c r="M25">
-        <v>21.8455104</v>
+        <v>23.543424</v>
       </c>
       <c r="N25">
-        <v>199.1024896</v>
+        <v>197.404576</v>
       </c>
       <c r="O25">
-        <v>39.82049792000001</v>
+        <v>39.48091520000001</v>
       </c>
       <c r="P25">
-        <v>159.28199168</v>
+        <v>157.9236608</v>
       </c>
       <c r="Q25">
-        <v>159.45899168</v>
+        <v>158.1006608</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.136236043728793</v>
+        <v>0.1372339036397363</v>
       </c>
       <c r="T25">
-        <v>0.990311746387435</v>
+        <v>1.001238721411019</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.11411479770232</v>
+        <v>9.384701222727841</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1145697667661996</v>
+        <v>0.1143937798612286</v>
       </c>
       <c r="C26">
-        <v>1659.054434942818</v>
+        <v>1646.040388070761</v>
       </c>
       <c r="D26">
-        <v>2074.318434942818</v>
+        <v>2079.640388070761</v>
       </c>
       <c r="E26">
-        <v>-688.736</v>
+        <v>-670.4</v>
       </c>
       <c r="F26">
-        <v>440.064</v>
+        <v>458.4</v>
       </c>
       <c r="G26">
         <v>24.8</v>
@@ -3419,28 +3419,28 @@
         <v>220.948</v>
       </c>
       <c r="M26">
-        <v>23.543424</v>
+        <v>24.5244</v>
       </c>
       <c r="N26">
-        <v>197.404576</v>
+        <v>196.4236</v>
       </c>
       <c r="O26">
-        <v>39.48091520000001</v>
+        <v>39.28472000000001</v>
       </c>
       <c r="P26">
-        <v>157.9236608</v>
+        <v>157.13888</v>
       </c>
       <c r="Q26">
-        <v>158.1006608</v>
+        <v>157.31588</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1372339036397363</v>
+        <v>0.1382583731483048</v>
       </c>
       <c r="T26">
-        <v>1.001238721411019</v>
+        <v>1.012457082435232</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.384701222727843</v>
+        <v>9.009313173818729</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1143937798612286</v>
+        <v>0.1142177929562576</v>
       </c>
       <c r="C27">
-        <v>1646.040388070761</v>
+        <v>1633.053719867875</v>
       </c>
       <c r="D27">
-        <v>2079.640388070761</v>
+        <v>2084.989719867875</v>
       </c>
       <c r="E27">
-        <v>-670.4</v>
+        <v>-652.064</v>
       </c>
       <c r="F27">
-        <v>458.4</v>
+        <v>476.736</v>
       </c>
       <c r="G27">
         <v>24.8</v>
@@ -3501,28 +3501,28 @@
         <v>220.948</v>
       </c>
       <c r="M27">
-        <v>24.5244</v>
+        <v>25.505376</v>
       </c>
       <c r="N27">
-        <v>196.4236</v>
+        <v>195.442624</v>
       </c>
       <c r="O27">
-        <v>39.28472000000001</v>
+        <v>39.08852480000001</v>
       </c>
       <c r="P27">
-        <v>157.13888</v>
+        <v>156.3540992</v>
       </c>
       <c r="Q27">
-        <v>157.31588</v>
+        <v>156.5310992</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1382583731483048</v>
+        <v>0.1393105310219697</v>
       </c>
       <c r="T27">
-        <v>1.012457082435232</v>
+        <v>1.023978642406046</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.009313173818729</v>
+        <v>8.662801128671855</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1142177929562576</v>
+        <v>0.1140418060512866</v>
       </c>
       <c r="C28">
-        <v>1633.053719867875</v>
+        <v>1620.094642152436</v>
       </c>
       <c r="D28">
-        <v>2084.989719867875</v>
+        <v>2090.366642152436</v>
       </c>
       <c r="E28">
-        <v>-652.064</v>
+        <v>-633.728</v>
       </c>
       <c r="F28">
-        <v>476.736</v>
+        <v>495.072</v>
       </c>
       <c r="G28">
         <v>24.8</v>
@@ -3583,28 +3583,28 @@
         <v>220.948</v>
       </c>
       <c r="M28">
-        <v>25.505376</v>
+        <v>26.486352</v>
       </c>
       <c r="N28">
-        <v>195.442624</v>
+        <v>194.461648</v>
       </c>
       <c r="O28">
-        <v>39.08852480000001</v>
+        <v>38.8923296</v>
       </c>
       <c r="P28">
-        <v>156.3540992</v>
+        <v>155.5693184</v>
       </c>
       <c r="Q28">
-        <v>156.5310992</v>
+        <v>155.7463184</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1393105310219697</v>
+        <v>0.1403915151387488</v>
       </c>
       <c r="T28">
-        <v>1.023978642406046</v>
+        <v>1.035815861554142</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.662801128671855</v>
+        <v>8.341956642424748</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1140418060512866</v>
+        <v>0.1138658191463156</v>
       </c>
       <c r="C29">
-        <v>1620.094642152436</v>
+        <v>1607.163368933382</v>
       </c>
       <c r="D29">
-        <v>2090.366642152436</v>
+        <v>2095.771368933381</v>
       </c>
       <c r="E29">
-        <v>-633.728</v>
+        <v>-615.3919999999999</v>
       </c>
       <c r="F29">
-        <v>495.072</v>
+        <v>513.408</v>
       </c>
       <c r="G29">
         <v>24.8</v>
@@ -3665,28 +3665,28 @@
         <v>220.948</v>
       </c>
       <c r="M29">
-        <v>26.486352</v>
+        <v>27.467328</v>
       </c>
       <c r="N29">
-        <v>194.461648</v>
+        <v>193.480672</v>
       </c>
       <c r="O29">
-        <v>38.8923296</v>
+        <v>38.69613440000001</v>
       </c>
       <c r="P29">
-        <v>155.5693184</v>
+        <v>154.7845376</v>
       </c>
       <c r="Q29">
-        <v>155.7463184</v>
+        <v>154.9615376</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1403915151387488</v>
+        <v>0.141502526592105</v>
       </c>
       <c r="T29">
-        <v>1.035815861554142</v>
+        <v>1.04798189234524</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.341956642424748</v>
+        <v>8.044029619481005</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1138658191463156</v>
+        <v>0.1136898322413446</v>
       </c>
       <c r="C30">
-        <v>1607.163368933382</v>
+        <v>1594.260116438697</v>
       </c>
       <c r="D30">
-        <v>2095.771368933381</v>
+        <v>2101.204116438697</v>
       </c>
       <c r="E30">
-        <v>-615.3919999999999</v>
+        <v>-597.0559999999999</v>
       </c>
       <c r="F30">
-        <v>513.408</v>
+        <v>531.744</v>
       </c>
       <c r="G30">
         <v>24.8</v>
@@ -3747,28 +3747,28 @@
         <v>220.948</v>
       </c>
       <c r="M30">
-        <v>27.467328</v>
+        <v>28.448304</v>
       </c>
       <c r="N30">
-        <v>193.480672</v>
+        <v>192.499696</v>
       </c>
       <c r="O30">
-        <v>38.69613440000001</v>
+        <v>38.4999392</v>
       </c>
       <c r="P30">
-        <v>154.7845376</v>
+        <v>153.9997568</v>
       </c>
       <c r="Q30">
-        <v>154.9615376</v>
+        <v>154.1767568</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.141502526592105</v>
+        <v>0.1426448341427388</v>
       </c>
       <c r="T30">
-        <v>1.04798189234524</v>
+        <v>1.060490628229046</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.044029619481005</v>
+        <v>7.766649287774765</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1136898322413446</v>
+        <v>0.1137058453363736</v>
       </c>
       <c r="C31">
-        <v>1594.260116438697</v>
+        <v>1575.428624761579</v>
       </c>
       <c r="D31">
-        <v>2101.204116438697</v>
+        <v>2100.708624761579</v>
       </c>
       <c r="E31">
-        <v>-597.056</v>
+        <v>-578.72</v>
       </c>
       <c r="F31">
-        <v>531.7439999999999</v>
+        <v>550.0799999999999</v>
       </c>
       <c r="G31">
         <v>24.8</v>
@@ -3829,45 +3829,45 @@
         <v>220.948</v>
       </c>
       <c r="M31">
-        <v>28.44830399999999</v>
+        <v>29.869344</v>
       </c>
       <c r="N31">
-        <v>192.499696</v>
+        <v>191.078656</v>
       </c>
       <c r="O31">
-        <v>38.49993920000001</v>
+        <v>38.21573120000001</v>
       </c>
       <c r="P31">
-        <v>153.9997568</v>
+        <v>152.8629248</v>
       </c>
       <c r="Q31">
-        <v>154.1767568</v>
+        <v>153.0399248</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1426448341427388</v>
+        <v>0.1438197790519622</v>
       </c>
       <c r="T31">
-        <v>1.060490628229046</v>
+        <v>1.073356756566675</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.766649287774768</v>
+        <v>7.397149398393217</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1137058453363736</v>
+        <v>0.1135362584314025</v>
       </c>
       <c r="C32">
-        <v>1575.428624761579</v>
+        <v>1562.352033565211</v>
       </c>
       <c r="D32">
-        <v>2100.708624761579</v>
+        <v>2105.968033565211</v>
       </c>
       <c r="E32">
-        <v>-578.72</v>
+        <v>-560.384</v>
       </c>
       <c r="F32">
-        <v>550.0799999999999</v>
+        <v>568.4159999999999</v>
       </c>
       <c r="G32">
         <v>24.8</v>
@@ -3911,28 +3911,28 @@
         <v>220.948</v>
       </c>
       <c r="M32">
-        <v>29.869344</v>
+        <v>30.8649888</v>
       </c>
       <c r="N32">
-        <v>191.078656</v>
+        <v>190.0830112</v>
       </c>
       <c r="O32">
-        <v>38.21573120000001</v>
+        <v>38.01660224</v>
       </c>
       <c r="P32">
-        <v>152.8629248</v>
+        <v>152.06640896</v>
       </c>
       <c r="Q32">
-        <v>153.0399248</v>
+        <v>152.24340896</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1438197790519622</v>
+        <v>0.145028780335366</v>
       </c>
       <c r="T32">
-        <v>1.073356756566675</v>
+        <v>1.086595816160467</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.397149398393217</v>
+        <v>7.158531675864403</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1135362584314025</v>
+        <v>0.1133666715264315</v>
       </c>
       <c r="C33">
-        <v>1562.352033565211</v>
+        <v>1549.301843754048</v>
       </c>
       <c r="D33">
-        <v>2105.968033565211</v>
+        <v>2111.253843754047</v>
       </c>
       <c r="E33">
-        <v>-560.384</v>
+        <v>-542.048</v>
       </c>
       <c r="F33">
-        <v>568.4159999999999</v>
+        <v>586.752</v>
       </c>
       <c r="G33">
         <v>24.8</v>
@@ -3993,28 +3993,28 @@
         <v>220.948</v>
       </c>
       <c r="M33">
-        <v>30.8649888</v>
+        <v>31.8606336</v>
       </c>
       <c r="N33">
-        <v>190.0830112</v>
+        <v>189.0873664</v>
       </c>
       <c r="O33">
-        <v>38.01660224</v>
+        <v>37.81747328</v>
       </c>
       <c r="P33">
-        <v>152.06640896</v>
+        <v>151.26989312</v>
       </c>
       <c r="Q33">
-        <v>152.24340896</v>
+        <v>151.44689312</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.145028780335366</v>
+        <v>0.1462733404800464</v>
       </c>
       <c r="T33">
-        <v>1.086595816160467</v>
+        <v>1.100224259859958</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.158531675864403</v>
+        <v>6.93482756099364</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1133666715264315</v>
+        <v>0.1131970846214605</v>
       </c>
       <c r="C34">
-        <v>1549.301843754048</v>
+        <v>1536.27825462436</v>
       </c>
       <c r="D34">
-        <v>2111.253843754047</v>
+        <v>2116.56625462436</v>
       </c>
       <c r="E34">
-        <v>-542.048</v>
+        <v>-523.712</v>
       </c>
       <c r="F34">
-        <v>586.752</v>
+        <v>605.088</v>
       </c>
       <c r="G34">
         <v>24.8</v>
@@ -4075,28 +4075,28 @@
         <v>220.948</v>
       </c>
       <c r="M34">
-        <v>31.8606336</v>
+        <v>32.8562784</v>
       </c>
       <c r="N34">
-        <v>189.0873664</v>
+        <v>188.0917216</v>
       </c>
       <c r="O34">
-        <v>37.81747328</v>
+        <v>37.61834432</v>
       </c>
       <c r="P34">
-        <v>151.26989312</v>
+        <v>150.47337728</v>
       </c>
       <c r="Q34">
-        <v>151.44689312</v>
+        <v>150.65037728</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1462733404800464</v>
+        <v>0.1475550516738217</v>
       </c>
       <c r="T34">
-        <v>1.100224259859958</v>
+        <v>1.11425952277436</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.93482756099364</v>
+        <v>6.72468127126656</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1131970846214605</v>
+        <v>0.1130274977164895</v>
       </c>
       <c r="C35">
-        <v>1536.27825462436</v>
+        <v>1523.281467483383</v>
       </c>
       <c r="D35">
-        <v>2116.56625462436</v>
+        <v>2121.905467483383</v>
       </c>
       <c r="E35">
-        <v>-523.712</v>
+        <v>-505.376</v>
       </c>
       <c r="F35">
-        <v>605.088</v>
+        <v>623.424</v>
       </c>
       <c r="G35">
         <v>24.8</v>
@@ -4157,28 +4157,28 @@
         <v>220.948</v>
       </c>
       <c r="M35">
-        <v>32.8562784</v>
+        <v>33.8519232</v>
       </c>
       <c r="N35">
-        <v>188.0917216</v>
+        <v>187.0960768</v>
       </c>
       <c r="O35">
-        <v>37.61834432</v>
+        <v>37.41921536</v>
       </c>
       <c r="P35">
-        <v>150.47337728</v>
+        <v>149.67686144</v>
       </c>
       <c r="Q35">
-        <v>150.65037728</v>
+        <v>149.85386144</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1475550516738217</v>
+        <v>0.1488756026007417</v>
       </c>
       <c r="T35">
-        <v>1.11425952277436</v>
+        <v>1.128720096686168</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.72468127126656</v>
+        <v>6.526896527994013</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1130274977164895</v>
+        <v>0.1128579108115185</v>
       </c>
       <c r="C36">
-        <v>1523.281467483383</v>
+        <v>1510.311685674746</v>
       </c>
       <c r="D36">
-        <v>2121.905467483383</v>
+        <v>2127.271685674746</v>
       </c>
       <c r="E36">
-        <v>-505.376</v>
+        <v>-487.04</v>
       </c>
       <c r="F36">
-        <v>623.424</v>
+        <v>641.76</v>
       </c>
       <c r="G36">
         <v>24.8</v>
@@ -4239,28 +4239,28 @@
         <v>220.948</v>
       </c>
       <c r="M36">
-        <v>33.8519232</v>
+        <v>34.847568</v>
       </c>
       <c r="N36">
-        <v>187.0960768</v>
+        <v>186.100432</v>
       </c>
       <c r="O36">
-        <v>37.41921536</v>
+        <v>37.22008640000001</v>
       </c>
       <c r="P36">
-        <v>149.67686144</v>
+        <v>148.8803456</v>
       </c>
       <c r="Q36">
-        <v>149.85386144</v>
+        <v>149.0573456</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1488756026007417</v>
+        <v>0.1502367858638747</v>
       </c>
       <c r="T36">
-        <v>1.128720096686168</v>
+        <v>1.143625611333724</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.526896527994013</v>
+        <v>6.340413770051327</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1128579108115185</v>
+        <v>0.1126883239065475</v>
       </c>
       <c r="C37">
-        <v>1510.311685674746</v>
+        <v>1497.369114604287</v>
       </c>
       <c r="D37">
-        <v>2127.271685674746</v>
+        <v>2132.665114604286</v>
       </c>
       <c r="E37">
-        <v>-487.04</v>
+        <v>-468.704</v>
       </c>
       <c r="F37">
-        <v>641.76</v>
+        <v>660.096</v>
       </c>
       <c r="G37">
         <v>24.8</v>
@@ -4321,28 +4321,28 @@
         <v>220.948</v>
       </c>
       <c r="M37">
-        <v>34.847568</v>
+        <v>35.8432128</v>
       </c>
       <c r="N37">
-        <v>186.100432</v>
+        <v>185.1047872</v>
       </c>
       <c r="O37">
-        <v>37.22008640000001</v>
+        <v>37.02095744</v>
       </c>
       <c r="P37">
-        <v>148.8803456</v>
+        <v>148.08382976</v>
       </c>
       <c r="Q37">
-        <v>149.0573456</v>
+        <v>148.26082976</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1502367858638747</v>
+        <v>0.1516405061039805</v>
       </c>
       <c r="T37">
-        <v>1.143625611333724</v>
+        <v>1.158996923314016</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.340413770051327</v>
+        <v>6.164291165327679</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1126883239065475</v>
+        <v>0.1128147370015765</v>
       </c>
       <c r="C38">
-        <v>1497.369114604286</v>
+        <v>1475.010166669847</v>
       </c>
       <c r="D38">
-        <v>2132.665114604285</v>
+        <v>2128.642166669847</v>
       </c>
       <c r="E38">
-        <v>-468.7040000000001</v>
+        <v>-450.3680000000001</v>
       </c>
       <c r="F38">
-        <v>660.0959999999999</v>
+        <v>678.4319999999999</v>
       </c>
       <c r="G38">
         <v>24.8</v>
@@ -4403,45 +4403,45 @@
         <v>220.948</v>
       </c>
       <c r="M38">
-        <v>35.8432128</v>
+        <v>37.5172896</v>
       </c>
       <c r="N38">
-        <v>185.1047872</v>
+        <v>183.4307104</v>
       </c>
       <c r="O38">
-        <v>37.02095744</v>
+        <v>36.68614208</v>
       </c>
       <c r="P38">
-        <v>148.08382976</v>
+        <v>146.74456832</v>
       </c>
       <c r="Q38">
-        <v>148.26082976</v>
+        <v>146.92156832</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1516405061039805</v>
+        <v>0.1530887888913913</v>
       </c>
       <c r="T38">
-        <v>1.158996923314016</v>
+        <v>1.174856213452412</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.16429116532768</v>
+        <v>5.889231401193759</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1128147370015765</v>
+        <v>0.1126531500966055</v>
       </c>
       <c r="C39">
-        <v>1475.010166669847</v>
+        <v>1461.819185251707</v>
       </c>
       <c r="D39">
-        <v>2128.642166669847</v>
+        <v>2133.787185251707</v>
       </c>
       <c r="E39">
-        <v>-450.3680000000001</v>
+        <v>-432.0319999999999</v>
       </c>
       <c r="F39">
-        <v>678.4319999999999</v>
+        <v>696.768</v>
       </c>
       <c r="G39">
         <v>24.8</v>
@@ -4485,28 +4485,28 @@
         <v>220.948</v>
       </c>
       <c r="M39">
-        <v>37.5172896</v>
+        <v>38.5312704</v>
       </c>
       <c r="N39">
-        <v>183.4307104</v>
+        <v>182.4167296</v>
       </c>
       <c r="O39">
-        <v>36.68614208</v>
+        <v>36.48334592</v>
       </c>
       <c r="P39">
-        <v>146.74456832</v>
+        <v>145.93338368</v>
       </c>
       <c r="Q39">
-        <v>146.92156832</v>
+        <v>146.11038368</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1530887888913913</v>
+        <v>0.154583790478396</v>
       </c>
       <c r="T39">
-        <v>1.174856213452412</v>
+        <v>1.191227093595273</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.889231401193759</v>
+        <v>5.734251627478132</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1126531500966055</v>
+        <v>0.1124915631916345</v>
       </c>
       <c r="C40">
-        <v>1461.819185251707</v>
+        <v>1448.653135551731</v>
       </c>
       <c r="D40">
-        <v>2133.787185251707</v>
+        <v>2138.957135551731</v>
       </c>
       <c r="E40">
-        <v>-432.0319999999999</v>
+        <v>-413.6959999999999</v>
       </c>
       <c r="F40">
-        <v>696.768</v>
+        <v>715.104</v>
       </c>
       <c r="G40">
         <v>24.8</v>
@@ -4567,28 +4567,28 @@
         <v>220.948</v>
       </c>
       <c r="M40">
-        <v>38.5312704</v>
+        <v>39.5452512</v>
       </c>
       <c r="N40">
-        <v>182.4167296</v>
+        <v>181.4027488</v>
       </c>
       <c r="O40">
-        <v>36.48334592</v>
+        <v>36.28054976000001</v>
       </c>
       <c r="P40">
-        <v>145.93338368</v>
+        <v>145.12219904</v>
       </c>
       <c r="Q40">
-        <v>146.11038368</v>
+        <v>145.29919904</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.154583790478396</v>
+        <v>0.1561278085108762</v>
       </c>
       <c r="T40">
-        <v>1.191227093595273</v>
+        <v>1.208134723906753</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.734251627478132</v>
+        <v>5.587219534465873</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1124915631916345</v>
+        <v>0.1123299762866635</v>
       </c>
       <c r="C41">
-        <v>1448.653135551731</v>
+        <v>1435.51219923115</v>
       </c>
       <c r="D41">
-        <v>2138.957135551731</v>
+        <v>2144.15219923115</v>
       </c>
       <c r="E41">
-        <v>-413.6959999999999</v>
+        <v>-395.3599999999999</v>
       </c>
       <c r="F41">
-        <v>715.104</v>
+        <v>733.4400000000001</v>
       </c>
       <c r="G41">
         <v>24.8</v>
@@ -4649,28 +4649,28 @@
         <v>220.948</v>
       </c>
       <c r="M41">
-        <v>39.5452512</v>
+        <v>40.559232</v>
       </c>
       <c r="N41">
-        <v>181.4027488</v>
+        <v>180.388768</v>
       </c>
       <c r="O41">
-        <v>36.28054976000001</v>
+        <v>36.0777536</v>
       </c>
       <c r="P41">
-        <v>145.12219904</v>
+        <v>144.3110144</v>
       </c>
       <c r="Q41">
-        <v>145.29919904</v>
+        <v>144.4880144</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1561278085108762</v>
+        <v>0.1577232938111058</v>
       </c>
       <c r="T41">
-        <v>1.208134723906753</v>
+        <v>1.225605941895281</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.587219534465873</v>
+        <v>5.447539046104226</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1123299762866635</v>
+        <v>0.1121683893816925</v>
       </c>
       <c r="C42">
-        <v>1435.51219923115</v>
+        <v>1422.396559720358</v>
       </c>
       <c r="D42">
-        <v>2144.15219923115</v>
+        <v>2149.372559720358</v>
       </c>
       <c r="E42">
-        <v>-395.3599999999999</v>
+        <v>-377.0239999999999</v>
       </c>
       <c r="F42">
-        <v>733.4400000000001</v>
+        <v>751.7760000000001</v>
       </c>
       <c r="G42">
         <v>24.8</v>
@@ -4731,28 +4731,28 @@
         <v>220.948</v>
       </c>
       <c r="M42">
-        <v>40.559232</v>
+        <v>41.57321280000001</v>
       </c>
       <c r="N42">
-        <v>180.388768</v>
+        <v>179.3747872</v>
       </c>
       <c r="O42">
-        <v>36.0777536</v>
+        <v>35.87495744</v>
       </c>
       <c r="P42">
-        <v>144.3110144</v>
+        <v>143.49982976</v>
       </c>
       <c r="Q42">
-        <v>144.4880144</v>
+        <v>143.67682976</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1577232938111058</v>
+        <v>0.1593728633588008</v>
       </c>
       <c r="T42">
-        <v>1.225605941895281</v>
+        <v>1.243669404561387</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.447539046104226</v>
+        <v>5.314672240101683</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1121683893816925</v>
+        <v>0.1120068024767215</v>
       </c>
       <c r="C43">
-        <v>1422.396559720358</v>
+        <v>1409.306402240497</v>
       </c>
       <c r="D43">
-        <v>2149.372559720358</v>
+        <v>2154.618402240497</v>
       </c>
       <c r="E43">
-        <v>-377.0239999999999</v>
+        <v>-358.6879999999999</v>
       </c>
       <c r="F43">
-        <v>751.7760000000001</v>
+        <v>770.1120000000001</v>
       </c>
       <c r="G43">
         <v>24.8</v>
@@ -4813,28 +4813,28 @@
         <v>220.948</v>
       </c>
       <c r="M43">
-        <v>41.57321280000001</v>
+        <v>42.58719360000001</v>
       </c>
       <c r="N43">
-        <v>179.3747872</v>
+        <v>178.3608064</v>
       </c>
       <c r="O43">
-        <v>35.87495744</v>
+        <v>35.67216128</v>
       </c>
       <c r="P43">
-        <v>143.49982976</v>
+        <v>142.68864512</v>
       </c>
       <c r="Q43">
-        <v>143.67682976</v>
+        <v>142.86564512</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1593728633588008</v>
+        <v>0.161079314615037</v>
       </c>
       <c r="T43">
-        <v>1.243669404561387</v>
+        <v>1.262355745250462</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.314672240101683</v>
+        <v>5.188132424861167</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1120068024767215</v>
+        <v>0.1118452155717505</v>
       </c>
       <c r="C44">
-        <v>1409.306402240496</v>
+        <v>1396.241913825364</v>
       </c>
       <c r="D44">
-        <v>2154.618402240496</v>
+        <v>2159.889913825364</v>
       </c>
       <c r="E44">
-        <v>-358.688</v>
+        <v>-340.352</v>
       </c>
       <c r="F44">
-        <v>770.112</v>
+        <v>788.448</v>
       </c>
       <c r="G44">
         <v>24.8</v>
@@ -4895,28 +4895,28 @@
         <v>220.948</v>
       </c>
       <c r="M44">
-        <v>42.5871936</v>
+        <v>43.6011744</v>
       </c>
       <c r="N44">
-        <v>178.3608064</v>
+        <v>177.3468256</v>
       </c>
       <c r="O44">
-        <v>35.67216128</v>
+        <v>35.46936512000001</v>
       </c>
       <c r="P44">
-        <v>142.68864512</v>
+        <v>141.87746048</v>
       </c>
       <c r="Q44">
-        <v>142.86564512</v>
+        <v>142.05446048</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.161079314615037</v>
+        <v>0.1628456413539482</v>
       </c>
       <c r="T44">
-        <v>1.262355745250462</v>
+        <v>1.281697747016347</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.188132424861168</v>
+        <v>5.067478182422536</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1118452155717505</v>
+        <v>0.1116836286667794</v>
       </c>
       <c r="C45">
-        <v>1396.241913825364</v>
+        <v>1383.203283343646</v>
       </c>
       <c r="D45">
-        <v>2159.889913825364</v>
+        <v>2165.187283343646</v>
       </c>
       <c r="E45">
-        <v>-340.352</v>
+        <v>-322.016</v>
       </c>
       <c r="F45">
-        <v>788.448</v>
+        <v>806.784</v>
       </c>
       <c r="G45">
         <v>24.8</v>
@@ -4977,28 +4977,28 @@
         <v>220.948</v>
       </c>
       <c r="M45">
-        <v>43.6011744</v>
+        <v>44.6151552</v>
       </c>
       <c r="N45">
-        <v>177.3468256</v>
+        <v>176.3328448</v>
       </c>
       <c r="O45">
-        <v>35.46936512000001</v>
+        <v>35.26656896</v>
       </c>
       <c r="P45">
-        <v>141.87746048</v>
+        <v>141.06627584</v>
       </c>
       <c r="Q45">
-        <v>142.05446048</v>
+        <v>141.24327584</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1628456413539482</v>
+        <v>0.1646750511906776</v>
       </c>
       <c r="T45">
-        <v>1.281697747016347</v>
+        <v>1.301730534559584</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.067478182422536</v>
+        <v>4.952308223731114</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1116836286667794</v>
+        <v>0.1115220417618084</v>
       </c>
       <c r="C46">
-        <v>1383.203283343646</v>
+        <v>1370.190701521464</v>
       </c>
       <c r="D46">
-        <v>2165.187283343646</v>
+        <v>2170.510701521463</v>
       </c>
       <c r="E46">
-        <v>-322.016</v>
+        <v>-303.6799999999999</v>
       </c>
       <c r="F46">
-        <v>806.784</v>
+        <v>825.12</v>
       </c>
       <c r="G46">
         <v>24.8</v>
@@ -5059,28 +5059,28 @@
         <v>220.948</v>
       </c>
       <c r="M46">
-        <v>44.6151552</v>
+        <v>45.629136</v>
       </c>
       <c r="N46">
-        <v>176.3328448</v>
+        <v>175.318864</v>
       </c>
       <c r="O46">
-        <v>35.26656896</v>
+        <v>35.0637728</v>
       </c>
       <c r="P46">
-        <v>141.06627584</v>
+        <v>140.2550912</v>
       </c>
       <c r="Q46">
-        <v>141.24327584</v>
+        <v>140.4320912</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1646750511906776</v>
+        <v>0.1665709850214699</v>
       </c>
       <c r="T46">
-        <v>1.301730534559584</v>
+        <v>1.322491787104394</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.952308223731114</v>
+        <v>4.842256929870423</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1115220417618084</v>
+        <v>0.1113604548568374</v>
       </c>
       <c r="C47">
-        <v>1370.190701521464</v>
+        <v>1357.204360965272</v>
       </c>
       <c r="D47">
-        <v>2170.510701521463</v>
+        <v>2175.860360965272</v>
       </c>
       <c r="E47">
-        <v>-303.6799999999999</v>
+        <v>-285.3439999999999</v>
       </c>
       <c r="F47">
-        <v>825.12</v>
+        <v>843.456</v>
       </c>
       <c r="G47">
         <v>24.8</v>
@@ -5141,28 +5141,28 @@
         <v>220.948</v>
       </c>
       <c r="M47">
-        <v>45.629136</v>
+        <v>46.6431168</v>
       </c>
       <c r="N47">
-        <v>175.318864</v>
+        <v>174.3048832</v>
       </c>
       <c r="O47">
-        <v>35.0637728</v>
+        <v>34.86097664</v>
       </c>
       <c r="P47">
-        <v>140.2550912</v>
+        <v>139.44390656</v>
       </c>
       <c r="Q47">
-        <v>140.4320912</v>
+        <v>139.62090656</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1665709850214699</v>
+        <v>0.168537138623773</v>
       </c>
       <c r="T47">
-        <v>1.322491787104394</v>
+        <v>1.344021974928642</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.842256929870423</v>
+        <v>4.73699047487324</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1113604548568374</v>
+        <v>0.1111988679518664</v>
       </c>
       <c r="C48">
-        <v>1357.204360965272</v>
+        <v>1344.244456185089</v>
       </c>
       <c r="D48">
-        <v>2175.860360965272</v>
+        <v>2181.236456185089</v>
       </c>
       <c r="E48">
-        <v>-285.3439999999999</v>
+        <v>-267.0079999999999</v>
       </c>
       <c r="F48">
-        <v>843.456</v>
+        <v>861.792</v>
       </c>
       <c r="G48">
         <v>24.8</v>
@@ -5223,28 +5223,28 @@
         <v>220.948</v>
       </c>
       <c r="M48">
-        <v>46.6431168</v>
+        <v>47.6570976</v>
       </c>
       <c r="N48">
-        <v>174.3048832</v>
+        <v>173.2909024</v>
       </c>
       <c r="O48">
-        <v>34.86097664</v>
+        <v>34.65818048</v>
       </c>
       <c r="P48">
-        <v>139.44390656</v>
+        <v>138.63272192</v>
       </c>
       <c r="Q48">
-        <v>139.62090656</v>
+        <v>138.80972192</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.168537138623773</v>
+        <v>0.1705774867016348</v>
       </c>
       <c r="T48">
-        <v>1.344021974928642</v>
+        <v>1.366364622670785</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.73699047487324</v>
+        <v>4.636203443492958</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1111988679518664</v>
+        <v>0.1110372810468954</v>
       </c>
       <c r="C49">
-        <v>1344.244456185089</v>
+        <v>1331.311183618066</v>
       </c>
       <c r="D49">
-        <v>2181.236456185089</v>
+        <v>2186.639183618066</v>
       </c>
       <c r="E49">
-        <v>-267.0079999999999</v>
+        <v>-248.6719999999999</v>
       </c>
       <c r="F49">
-        <v>861.792</v>
+        <v>880.128</v>
       </c>
       <c r="G49">
         <v>24.8</v>
@@ -5305,28 +5305,28 @@
         <v>220.948</v>
       </c>
       <c r="M49">
-        <v>47.6570976</v>
+        <v>48.67107840000001</v>
       </c>
       <c r="N49">
-        <v>173.2909024</v>
+        <v>172.2769216</v>
       </c>
       <c r="O49">
-        <v>34.65818048</v>
+        <v>34.45538432</v>
       </c>
       <c r="P49">
-        <v>138.63272192</v>
+        <v>137.82153728</v>
       </c>
       <c r="Q49">
-        <v>138.80972192</v>
+        <v>137.99853728</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1705774867016348</v>
+        <v>0.1726963097055681</v>
       </c>
       <c r="T49">
-        <v>1.366364622670785</v>
+        <v>1.389566603018396</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.636203443492958</v>
+        <v>4.539615871753521</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1110372810468954</v>
+        <v>0.1118556941419244</v>
       </c>
       <c r="C50">
-        <v>1331.311183618067</v>
+        <v>1285.883285406664</v>
       </c>
       <c r="D50">
-        <v>2186.639183618066</v>
+        <v>2159.547285406664</v>
       </c>
       <c r="E50">
-        <v>-248.672</v>
+        <v>-230.336</v>
       </c>
       <c r="F50">
-        <v>880.1279999999999</v>
+        <v>898.4639999999999</v>
       </c>
       <c r="G50">
         <v>24.8</v>
@@ -5387,45 +5387,45 @@
         <v>220.948</v>
       </c>
       <c r="M50">
-        <v>48.6710784</v>
+        <v>51.9312192</v>
       </c>
       <c r="N50">
-        <v>172.2769216</v>
+        <v>169.0167808</v>
       </c>
       <c r="O50">
-        <v>34.45538432</v>
+        <v>33.80335616</v>
       </c>
       <c r="P50">
-        <v>137.82153728</v>
+        <v>135.21342464</v>
       </c>
       <c r="Q50">
-        <v>137.99853728</v>
+        <v>135.39042464</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1726963097055681</v>
+        <v>0.1748982238076949</v>
       </c>
       <c r="T50">
-        <v>1.389566603018396</v>
+        <v>1.413678464948265</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.2</v>
       </c>
       <c r="W50">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.539615871753522</v>
+        <v>4.254627628692376</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1118556941419244</v>
+        <v>0.1117141072369534</v>
       </c>
       <c r="C51">
-        <v>1285.883285406664</v>
+        <v>1272.186104456129</v>
       </c>
       <c r="D51">
-        <v>2159.547285406664</v>
+        <v>2164.186104456129</v>
       </c>
       <c r="E51">
-        <v>-230.336</v>
+        <v>-212</v>
       </c>
       <c r="F51">
-        <v>898.4639999999999</v>
+        <v>916.8</v>
       </c>
       <c r="G51">
         <v>24.8</v>
@@ -5469,28 +5469,28 @@
         <v>220.948</v>
       </c>
       <c r="M51">
-        <v>51.9312192</v>
+        <v>52.99104</v>
       </c>
       <c r="N51">
-        <v>169.0167808</v>
+        <v>167.95696</v>
       </c>
       <c r="O51">
-        <v>33.80335616</v>
+        <v>33.59139200000001</v>
       </c>
       <c r="P51">
-        <v>135.21342464</v>
+        <v>134.365568</v>
       </c>
       <c r="Q51">
-        <v>135.39042464</v>
+        <v>134.542568</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1748982238076949</v>
+        <v>0.1771882144739068</v>
       </c>
       <c r="T51">
-        <v>1.413678464948265</v>
+        <v>1.43875480135533</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.254627628692376</v>
+        <v>4.169535076118529</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1117141072369534</v>
+        <v>0.1115725203319824</v>
       </c>
       <c r="C52">
-        <v>1272.186104456129</v>
+        <v>1258.508895251503</v>
       </c>
       <c r="D52">
-        <v>2164.186104456129</v>
+        <v>2168.844895251503</v>
       </c>
       <c r="E52">
-        <v>-212</v>
+        <v>-193.664</v>
       </c>
       <c r="F52">
-        <v>916.8</v>
+        <v>935.136</v>
       </c>
       <c r="G52">
         <v>24.8</v>
@@ -5551,28 +5551,28 @@
         <v>220.948</v>
       </c>
       <c r="M52">
-        <v>52.99104</v>
+        <v>54.0508608</v>
       </c>
       <c r="N52">
-        <v>167.95696</v>
+        <v>166.8971392</v>
       </c>
       <c r="O52">
-        <v>33.59139200000001</v>
+        <v>33.37942784</v>
       </c>
       <c r="P52">
-        <v>134.365568</v>
+        <v>133.51771136</v>
       </c>
       <c r="Q52">
-        <v>134.542568</v>
+        <v>133.69471136</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1771882144739068</v>
+        <v>0.1795716741469029</v>
       </c>
       <c r="T52">
-        <v>1.43875480135533</v>
+        <v>1.464854661697377</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.169535076118529</v>
+        <v>4.087779486390714</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1115725203319824</v>
+        <v>0.1114309334270114</v>
       </c>
       <c r="C53">
-        <v>1258.508895251503</v>
+        <v>1244.851787049109</v>
       </c>
       <c r="D53">
-        <v>2168.844895251503</v>
+        <v>2173.523787049109</v>
       </c>
       <c r="E53">
-        <v>-193.664</v>
+        <v>-175.328</v>
       </c>
       <c r="F53">
-        <v>935.136</v>
+        <v>953.472</v>
       </c>
       <c r="G53">
         <v>24.8</v>
@@ -5633,28 +5633,28 @@
         <v>220.948</v>
       </c>
       <c r="M53">
-        <v>54.0508608</v>
+        <v>55.1106816</v>
       </c>
       <c r="N53">
-        <v>166.8971392</v>
+        <v>165.8373184</v>
       </c>
       <c r="O53">
-        <v>33.37942784</v>
+        <v>33.16746368</v>
       </c>
       <c r="P53">
-        <v>133.51771136</v>
+        <v>132.66985472</v>
       </c>
       <c r="Q53">
-        <v>133.69471136</v>
+        <v>132.84685472</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1795716741469029</v>
+        <v>0.1820544446396071</v>
       </c>
       <c r="T53">
-        <v>1.464854661697377</v>
+        <v>1.492042016220342</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.087779486390714</v>
+        <v>4.009168342421662</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1114309334270114</v>
+        <v>0.1127733465220404</v>
       </c>
       <c r="C54">
-        <v>1244.851787049109</v>
+        <v>1182.949697767136</v>
       </c>
       <c r="D54">
-        <v>2173.523787049109</v>
+        <v>2129.957697767136</v>
       </c>
       <c r="E54">
-        <v>-175.328</v>
+        <v>-156.992</v>
       </c>
       <c r="F54">
-        <v>953.472</v>
+        <v>971.808</v>
       </c>
       <c r="G54">
         <v>24.8</v>
@@ -5715,45 +5715,45 @@
         <v>220.948</v>
       </c>
       <c r="M54">
-        <v>55.1106816</v>
+        <v>59.5718304</v>
       </c>
       <c r="N54">
-        <v>165.8373184</v>
+        <v>161.3761696</v>
       </c>
       <c r="O54">
-        <v>33.16746368</v>
+        <v>32.27523392</v>
       </c>
       <c r="P54">
-        <v>132.66985472</v>
+        <v>129.10093568</v>
       </c>
       <c r="Q54">
-        <v>132.84685472</v>
+        <v>129.27793568</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1820544446396071</v>
+        <v>0.1846428649405115</v>
       </c>
       <c r="T54">
-        <v>1.492042016220342</v>
+        <v>1.520386279446413</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.009168342421662</v>
+        <v>3.708934214651897</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1127733465220404</v>
+        <v>0.1126597596170694</v>
       </c>
       <c r="C55">
-        <v>1182.949697767136</v>
+        <v>1168.232246562319</v>
       </c>
       <c r="D55">
-        <v>2129.957697767136</v>
+        <v>2133.576246562319</v>
       </c>
       <c r="E55">
-        <v>-156.992</v>
+        <v>-138.6559999999999</v>
       </c>
       <c r="F55">
-        <v>971.808</v>
+        <v>990.144</v>
       </c>
       <c r="G55">
         <v>24.8</v>
@@ -5797,28 +5797,28 @@
         <v>220.948</v>
       </c>
       <c r="M55">
-        <v>59.5718304</v>
+        <v>60.6958272</v>
       </c>
       <c r="N55">
-        <v>161.3761696</v>
+        <v>160.2521728</v>
       </c>
       <c r="O55">
-        <v>32.27523392</v>
+        <v>32.05043456000001</v>
       </c>
       <c r="P55">
-        <v>129.10093568</v>
+        <v>128.20173824</v>
       </c>
       <c r="Q55">
-        <v>129.27793568</v>
+        <v>128.37873824</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1846428649405115</v>
+        <v>0.1873438252544987</v>
       </c>
       <c r="T55">
-        <v>1.520386279446413</v>
+        <v>1.549962901943182</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.708934214651897</v>
+        <v>3.640250247713899</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1126597596170694</v>
+        <v>0.1125461727120984</v>
       </c>
       <c r="C56">
-        <v>1168.232246562319</v>
+        <v>1153.527111262411</v>
       </c>
       <c r="D56">
-        <v>2133.576246562319</v>
+        <v>2137.207111262411</v>
       </c>
       <c r="E56">
-        <v>-138.6559999999999</v>
+        <v>-120.3199999999999</v>
       </c>
       <c r="F56">
-        <v>990.144</v>
+        <v>1008.48</v>
       </c>
       <c r="G56">
         <v>24.8</v>
@@ -5879,28 +5879,28 @@
         <v>220.948</v>
       </c>
       <c r="M56">
-        <v>60.6958272</v>
+        <v>61.819824</v>
       </c>
       <c r="N56">
-        <v>160.2521728</v>
+        <v>159.128176</v>
       </c>
       <c r="O56">
-        <v>32.05043456000001</v>
+        <v>31.8256352</v>
       </c>
       <c r="P56">
-        <v>128.20173824</v>
+        <v>127.3025408</v>
       </c>
       <c r="Q56">
-        <v>128.37873824</v>
+        <v>127.4795408</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1873438252544987</v>
+        <v>0.1901648282491075</v>
       </c>
       <c r="T56">
-        <v>1.549962901943182</v>
+        <v>1.580854040995363</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.640250247713899</v>
+        <v>3.574063879573646</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1125461727120984</v>
+        <v>0.1124325858071274</v>
       </c>
       <c r="C57">
-        <v>1153.527111262411</v>
+        <v>1138.834354851262</v>
       </c>
       <c r="D57">
-        <v>2137.207111262411</v>
+        <v>2140.850354851262</v>
       </c>
       <c r="E57">
-        <v>-120.3199999999999</v>
+        <v>-101.9839999999999</v>
       </c>
       <c r="F57">
-        <v>1008.48</v>
+        <v>1026.816</v>
       </c>
       <c r="G57">
         <v>24.8</v>
@@ -5961,28 +5961,28 @@
         <v>220.948</v>
       </c>
       <c r="M57">
-        <v>61.819824</v>
+        <v>62.9438208</v>
       </c>
       <c r="N57">
-        <v>159.128176</v>
+        <v>158.0041792</v>
       </c>
       <c r="O57">
-        <v>31.8256352</v>
+        <v>31.60083584</v>
       </c>
       <c r="P57">
-        <v>127.3025408</v>
+        <v>126.40334336</v>
       </c>
       <c r="Q57">
-        <v>127.4795408</v>
+        <v>126.58034336</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1901648282491075</v>
+        <v>0.1931140586525622</v>
       </c>
       <c r="T57">
-        <v>1.580854040995363</v>
+        <v>1.613149322731734</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.574063879573646</v>
+        <v>3.510241310295545</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1124325858071274</v>
+        <v>0.1135957989021564</v>
       </c>
       <c r="C58">
-        <v>1138.834354851262</v>
+        <v>1083.766504093747</v>
       </c>
       <c r="D58">
-        <v>2140.850354851262</v>
+        <v>2104.118504093747</v>
       </c>
       <c r="E58">
-        <v>-101.9839999999999</v>
+        <v>-83.64799999999991</v>
       </c>
       <c r="F58">
-        <v>1026.816</v>
+        <v>1045.152</v>
       </c>
       <c r="G58">
         <v>24.8</v>
@@ -6043,45 +6043,45 @@
         <v>220.948</v>
       </c>
       <c r="M58">
-        <v>62.9438208</v>
+        <v>66.99424320000001</v>
       </c>
       <c r="N58">
-        <v>158.0041792</v>
+        <v>153.9537568</v>
       </c>
       <c r="O58">
-        <v>31.60083584</v>
+        <v>30.79075136</v>
       </c>
       <c r="P58">
-        <v>126.40334336</v>
+        <v>123.16300544</v>
       </c>
       <c r="Q58">
-        <v>126.58034336</v>
+        <v>123.34000544</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1931140586525622</v>
+        <v>0.1962004625631543</v>
       </c>
       <c r="T58">
-        <v>1.613149322731734</v>
+        <v>1.646946710595378</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.510241310295545</v>
+        <v>3.298014716583887</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1135957989021564</v>
+        <v>0.1135046119971854</v>
       </c>
       <c r="C59">
-        <v>1083.766504093747</v>
+        <v>1068.264403416418</v>
       </c>
       <c r="D59">
-        <v>2104.118504093747</v>
+        <v>2106.952403416418</v>
       </c>
       <c r="E59">
-        <v>-83.64799999999991</v>
+        <v>-65.3119999999999</v>
       </c>
       <c r="F59">
-        <v>1045.152</v>
+        <v>1063.488</v>
       </c>
       <c r="G59">
         <v>24.8</v>
@@ -6125,28 +6125,28 @@
         <v>220.948</v>
       </c>
       <c r="M59">
-        <v>66.99424320000001</v>
+        <v>68.16958080000001</v>
       </c>
       <c r="N59">
-        <v>153.9537568</v>
+        <v>152.7784192</v>
       </c>
       <c r="O59">
-        <v>30.79075136</v>
+        <v>30.55568384</v>
       </c>
       <c r="P59">
-        <v>123.16300544</v>
+        <v>122.22273536</v>
       </c>
       <c r="Q59">
-        <v>123.34000544</v>
+        <v>122.39973536</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1962004625631543</v>
+        <v>0.1994338380885366</v>
       </c>
       <c r="T59">
-        <v>1.646946710595378</v>
+        <v>1.682353497881101</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.298014716583887</v>
+        <v>3.241152393884165</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1135046119971853</v>
+        <v>0.1134134250922144</v>
       </c>
       <c r="C60">
-        <v>1068.264403416419</v>
+        <v>1052.769946620697</v>
       </c>
       <c r="D60">
-        <v>2106.952403416419</v>
+        <v>2109.793946620696</v>
       </c>
       <c r="E60">
-        <v>-65.31200000000013</v>
+        <v>-46.97600000000011</v>
       </c>
       <c r="F60">
-        <v>1063.488</v>
+        <v>1081.824</v>
       </c>
       <c r="G60">
         <v>24.8</v>
@@ -6207,28 +6207,28 @@
         <v>220.948</v>
       </c>
       <c r="M60">
-        <v>68.16958079999999</v>
+        <v>69.3449184</v>
       </c>
       <c r="N60">
-        <v>152.7784192</v>
+        <v>151.6030816</v>
       </c>
       <c r="O60">
-        <v>30.55568384000001</v>
+        <v>30.32061632</v>
       </c>
       <c r="P60">
-        <v>122.22273536</v>
+        <v>121.28246528</v>
       </c>
       <c r="Q60">
-        <v>122.39973536</v>
+        <v>121.45946528</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1994338380885365</v>
+        <v>0.2028249392493033</v>
       </c>
       <c r="T60">
-        <v>1.6823534978811</v>
+        <v>1.719487445522224</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.241152393884166</v>
+        <v>3.186217607547145</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1134134250922144</v>
+        <v>0.1133222381872433</v>
       </c>
       <c r="C61">
-        <v>1052.769946620697</v>
+        <v>1037.283164675132</v>
       </c>
       <c r="D61">
-        <v>2109.793946620696</v>
+        <v>2112.643164675131</v>
       </c>
       <c r="E61">
-        <v>-46.97600000000011</v>
+        <v>-28.6400000000001</v>
       </c>
       <c r="F61">
-        <v>1081.824</v>
+        <v>1100.16</v>
       </c>
       <c r="G61">
         <v>24.8</v>
@@ -6289,28 +6289,28 @@
         <v>220.948</v>
       </c>
       <c r="M61">
-        <v>69.3449184</v>
+        <v>70.52025599999999</v>
       </c>
       <c r="N61">
-        <v>151.6030816</v>
+        <v>150.427744</v>
       </c>
       <c r="O61">
-        <v>30.32061632</v>
+        <v>30.08554880000001</v>
       </c>
       <c r="P61">
-        <v>121.28246528</v>
+        <v>120.3421952</v>
       </c>
       <c r="Q61">
-        <v>121.45946528</v>
+        <v>120.5191952</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2028249392493033</v>
+        <v>0.2063855954681083</v>
       </c>
       <c r="T61">
-        <v>1.719487445522224</v>
+        <v>1.758478090545403</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.186217607547145</v>
+        <v>3.133113980754693</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1133222381872433</v>
+        <v>0.1132310512822723</v>
       </c>
       <c r="C62">
-        <v>1037.283164675132</v>
+        <v>1021.804088715785</v>
       </c>
       <c r="D62">
-        <v>2112.643164675131</v>
+        <v>2115.500088715784</v>
       </c>
       <c r="E62">
-        <v>-28.6400000000001</v>
+        <v>-10.30400000000009</v>
       </c>
       <c r="F62">
-        <v>1100.16</v>
+        <v>1118.496</v>
       </c>
       <c r="G62">
         <v>24.8</v>
@@ -6371,28 +6371,28 @@
         <v>220.948</v>
       </c>
       <c r="M62">
-        <v>70.52025599999999</v>
+        <v>71.6955936</v>
       </c>
       <c r="N62">
-        <v>150.427744</v>
+        <v>149.2524064</v>
       </c>
       <c r="O62">
-        <v>30.08554880000001</v>
+        <v>29.85048128</v>
       </c>
       <c r="P62">
-        <v>120.3421952</v>
+        <v>119.40192512</v>
       </c>
       <c r="Q62">
-        <v>120.5191952</v>
+        <v>119.57892512</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2063855954681083</v>
+        <v>0.2101288494417239</v>
       </c>
       <c r="T62">
-        <v>1.758478090545403</v>
+        <v>1.799468255826182</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.133113980754693</v>
+        <v>3.081751456480026</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1132310512822723</v>
+        <v>0.1131398643773013</v>
       </c>
       <c r="C63">
-        <v>1021.804088715785</v>
+        <v>1006.332750047371</v>
       </c>
       <c r="D63">
-        <v>2115.500088715784</v>
+        <v>2118.364750047371</v>
       </c>
       <c r="E63">
-        <v>-10.30400000000009</v>
+        <v>8.031999999999925</v>
       </c>
       <c r="F63">
-        <v>1118.496</v>
+        <v>1136.832</v>
       </c>
       <c r="G63">
         <v>24.8</v>
@@ -6453,28 +6453,28 @@
         <v>220.948</v>
       </c>
       <c r="M63">
-        <v>71.6955936</v>
+        <v>72.8709312</v>
       </c>
       <c r="N63">
-        <v>149.2524064</v>
+        <v>148.0770688</v>
       </c>
       <c r="O63">
-        <v>29.85048128</v>
+        <v>29.61541376</v>
       </c>
       <c r="P63">
-        <v>119.40192512</v>
+        <v>118.46165504</v>
       </c>
       <c r="Q63">
-        <v>119.57892512</v>
+        <v>118.63865504</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2101288494417239</v>
+        <v>0.2140691167823719</v>
       </c>
       <c r="T63">
-        <v>1.799468255826182</v>
+        <v>1.842615798227002</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.081751456480026</v>
+        <v>3.032045787827122</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1131398643773013</v>
+        <v>0.1169798774723303</v>
       </c>
       <c r="C64">
-        <v>1006.332750047371</v>
+        <v>873.7151768121273</v>
       </c>
       <c r="D64">
-        <v>2118.364750047371</v>
+        <v>2004.083176812127</v>
       </c>
       <c r="E64">
-        <v>8.031999999999925</v>
+        <v>26.36799999999994</v>
       </c>
       <c r="F64">
-        <v>1136.832</v>
+        <v>1155.168</v>
       </c>
       <c r="G64">
         <v>24.8</v>
@@ -6535,45 +6535,45 @@
         <v>220.948</v>
       </c>
       <c r="M64">
-        <v>72.8709312</v>
+        <v>83.0565792</v>
       </c>
       <c r="N64">
-        <v>148.0770688</v>
+        <v>137.8914208</v>
       </c>
       <c r="O64">
-        <v>29.61541376</v>
+        <v>27.57828416</v>
       </c>
       <c r="P64">
-        <v>118.46165504</v>
+        <v>110.31313664</v>
       </c>
       <c r="Q64">
-        <v>118.63865504</v>
+        <v>110.49013664</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2140691167823719</v>
+        <v>0.2182223715468387</v>
       </c>
       <c r="T64">
-        <v>1.842615798227002</v>
+        <v>1.888095640217055</v>
       </c>
       <c r="U64">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.032045787827122</v>
+        <v>2.660210691653431</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1169798774723303</v>
+        <v>0.1169510905673593</v>
       </c>
       <c r="C65">
-        <v>873.7151768121273</v>
+        <v>856.1900055921908</v>
       </c>
       <c r="D65">
-        <v>2004.083176812127</v>
+        <v>2004.894005592191</v>
       </c>
       <c r="E65">
-        <v>26.36799999999994</v>
+        <v>44.70399999999995</v>
       </c>
       <c r="F65">
-        <v>1155.168</v>
+        <v>1173.504</v>
       </c>
       <c r="G65">
         <v>24.8</v>
@@ -6617,28 +6617,28 @@
         <v>220.948</v>
       </c>
       <c r="M65">
-        <v>83.0565792</v>
+        <v>84.3749376</v>
       </c>
       <c r="N65">
-        <v>137.8914208</v>
+        <v>136.5730624</v>
       </c>
       <c r="O65">
-        <v>27.57828416</v>
+        <v>27.31461248000001</v>
       </c>
       <c r="P65">
-        <v>110.31313664</v>
+        <v>109.25844992</v>
       </c>
       <c r="Q65">
-        <v>110.49013664</v>
+        <v>109.43544992</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2182223715468387</v>
+        <v>0.2226063626871092</v>
       </c>
       <c r="T65">
-        <v>1.888095640217055</v>
+        <v>1.936102140095444</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.660210691653431</v>
+        <v>2.618644899596347</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1169510905673593</v>
+        <v>0.1169223036623883</v>
       </c>
       <c r="C66">
-        <v>856.1900055921908</v>
+        <v>838.6654907416303</v>
       </c>
       <c r="D66">
-        <v>2004.894005592191</v>
+        <v>2005.70549074163</v>
       </c>
       <c r="E66">
-        <v>44.70399999999995</v>
+        <v>63.03999999999996</v>
       </c>
       <c r="F66">
-        <v>1173.504</v>
+        <v>1191.84</v>
       </c>
       <c r="G66">
         <v>24.8</v>
@@ -6699,28 +6699,28 @@
         <v>220.948</v>
       </c>
       <c r="M66">
-        <v>84.3749376</v>
+        <v>85.693296</v>
       </c>
       <c r="N66">
-        <v>136.5730624</v>
+        <v>135.254704</v>
       </c>
       <c r="O66">
-        <v>27.31461248000001</v>
+        <v>27.0509408</v>
       </c>
       <c r="P66">
-        <v>109.25844992</v>
+        <v>108.2037632</v>
       </c>
       <c r="Q66">
-        <v>109.43544992</v>
+        <v>108.3807632</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2226063626871092</v>
+        <v>0.2272408676068237</v>
       </c>
       <c r="T66">
-        <v>1.936102140095444</v>
+        <v>1.986851868538313</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.618644899596347</v>
+        <v>2.578358054987172</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1169223036623883</v>
+        <v>0.1168935167574173</v>
       </c>
       <c r="C67">
-        <v>838.6654907416303</v>
+        <v>821.1416330577686</v>
       </c>
       <c r="D67">
-        <v>2005.70549074163</v>
+        <v>2006.517633057769</v>
       </c>
       <c r="E67">
-        <v>63.03999999999996</v>
+        <v>81.37599999999998</v>
       </c>
       <c r="F67">
-        <v>1191.84</v>
+        <v>1210.176</v>
       </c>
       <c r="G67">
         <v>24.8</v>
@@ -6781,28 +6781,28 @@
         <v>220.948</v>
       </c>
       <c r="M67">
-        <v>85.693296</v>
+        <v>87.0116544</v>
       </c>
       <c r="N67">
-        <v>135.254704</v>
+        <v>133.9363456</v>
       </c>
       <c r="O67">
-        <v>27.0509408</v>
+        <v>26.78726912</v>
       </c>
       <c r="P67">
-        <v>108.2037632</v>
+        <v>107.14907648</v>
       </c>
       <c r="Q67">
-        <v>108.3807632</v>
+        <v>107.32607648</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2272408676068237</v>
+        <v>0.232147990462992</v>
       </c>
       <c r="T67">
-        <v>1.986851868538313</v>
+        <v>2.04058687512488</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.578358054987172</v>
+        <v>2.539292023851003</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1168935167574173</v>
+        <v>0.1168647298524463</v>
       </c>
       <c r="C68">
-        <v>821.1416330577686</v>
+        <v>803.6184333392216</v>
       </c>
       <c r="D68">
-        <v>2006.517633057769</v>
+        <v>2007.330433339222</v>
       </c>
       <c r="E68">
-        <v>81.37599999999998</v>
+        <v>99.71199999999999</v>
       </c>
       <c r="F68">
-        <v>1210.176</v>
+        <v>1228.512</v>
       </c>
       <c r="G68">
         <v>24.8</v>
@@ -6863,28 +6863,28 @@
         <v>220.948</v>
       </c>
       <c r="M68">
-        <v>87.0116544</v>
+        <v>88.33001280000001</v>
       </c>
       <c r="N68">
-        <v>133.9363456</v>
+        <v>132.6179872</v>
       </c>
       <c r="O68">
-        <v>26.78726912</v>
+        <v>26.52359744</v>
       </c>
       <c r="P68">
-        <v>107.14907648</v>
+        <v>106.09438976</v>
       </c>
       <c r="Q68">
-        <v>107.32607648</v>
+        <v>106.27138976</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.232147990462992</v>
+        <v>0.2373525147043827</v>
       </c>
       <c r="T68">
-        <v>2.04058687512488</v>
+        <v>2.0975785487773</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.539292023851003</v>
+        <v>2.501392142898003</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1168647298524463</v>
+        <v>0.1189575429474753</v>
       </c>
       <c r="C69">
-        <v>803.6184333392216</v>
+        <v>727.8588615831466</v>
       </c>
       <c r="D69">
-        <v>2007.330433339222</v>
+        <v>1949.906861583147</v>
       </c>
       <c r="E69">
-        <v>99.71199999999999</v>
+        <v>118.048</v>
       </c>
       <c r="F69">
-        <v>1228.512</v>
+        <v>1246.848</v>
       </c>
       <c r="G69">
         <v>24.8</v>
@@ -6945,45 +6945,45 @@
         <v>220.948</v>
       </c>
       <c r="M69">
-        <v>88.33001280000001</v>
+        <v>94.5110784</v>
       </c>
       <c r="N69">
-        <v>132.6179872</v>
+        <v>126.4369216</v>
       </c>
       <c r="O69">
-        <v>26.52359744</v>
+        <v>25.28738432</v>
       </c>
       <c r="P69">
-        <v>106.09438976</v>
+        <v>101.14953728</v>
       </c>
       <c r="Q69">
-        <v>106.27138976</v>
+        <v>101.32653728</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2373525147043827</v>
+        <v>0.2428823217108602</v>
       </c>
       <c r="T69">
-        <v>2.0975785487773</v>
+        <v>2.158132202032995</v>
       </c>
       <c r="U69">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.2</v>
       </c>
       <c r="W69">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.501392142898003</v>
+        <v>2.337800009697064</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1189575429474753</v>
+        <v>0.1189599560425043</v>
       </c>
       <c r="C70">
-        <v>727.8588615831466</v>
+        <v>709.4585462006714</v>
       </c>
       <c r="D70">
-        <v>1949.906861583147</v>
+        <v>1949.842546200671</v>
       </c>
       <c r="E70">
-        <v>118.048</v>
+        <v>136.384</v>
       </c>
       <c r="F70">
-        <v>1246.848</v>
+        <v>1265.184</v>
       </c>
       <c r="G70">
         <v>24.8</v>
@@ -7027,28 +7027,28 @@
         <v>220.948</v>
       </c>
       <c r="M70">
-        <v>94.5110784</v>
+        <v>95.9009472</v>
       </c>
       <c r="N70">
-        <v>126.4369216</v>
+        <v>125.0470528</v>
       </c>
       <c r="O70">
-        <v>25.28738432</v>
+        <v>25.00941056</v>
       </c>
       <c r="P70">
-        <v>101.14953728</v>
+        <v>100.03764224</v>
       </c>
       <c r="Q70">
-        <v>101.32653728</v>
+        <v>100.21464224</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2428823217108602</v>
+        <v>0.2487688904596912</v>
       </c>
       <c r="T70">
-        <v>2.158132202032995</v>
+        <v>2.22259254259551</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.337800009697064</v>
+        <v>2.303918850136237</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1189599560425043</v>
+        <v>0.1189623691375332</v>
       </c>
       <c r="C71">
-        <v>709.4585462006714</v>
+        <v>691.0582350607922</v>
       </c>
       <c r="D71">
-        <v>1949.842546200671</v>
+        <v>1949.778235060792</v>
       </c>
       <c r="E71">
-        <v>136.384</v>
+        <v>154.72</v>
       </c>
       <c r="F71">
-        <v>1265.184</v>
+        <v>1283.52</v>
       </c>
       <c r="G71">
         <v>24.8</v>
@@ -7109,28 +7109,28 @@
         <v>220.948</v>
       </c>
       <c r="M71">
-        <v>95.9009472</v>
+        <v>97.29081600000001</v>
       </c>
       <c r="N71">
-        <v>125.0470528</v>
+        <v>123.657184</v>
       </c>
       <c r="O71">
-        <v>25.00941056</v>
+        <v>24.7314368</v>
       </c>
       <c r="P71">
-        <v>100.03764224</v>
+        <v>98.9257472</v>
       </c>
       <c r="Q71">
-        <v>100.21464224</v>
+        <v>99.10274720000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2487688904596912</v>
+        <v>0.2550478971251109</v>
       </c>
       <c r="T71">
-        <v>2.22259254259551</v>
+        <v>2.291350239195526</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.303918850136237</v>
+        <v>2.27100572370572</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1189623691375332</v>
+        <v>0.1189647822325623</v>
       </c>
       <c r="C72">
-        <v>691.0582350607922</v>
+        <v>672.6579281630864</v>
       </c>
       <c r="D72">
-        <v>1949.778235060792</v>
+        <v>1949.713928163086</v>
       </c>
       <c r="E72">
-        <v>154.72</v>
+        <v>173.056</v>
       </c>
       <c r="F72">
-        <v>1283.52</v>
+        <v>1301.856</v>
       </c>
       <c r="G72">
         <v>24.8</v>
@@ -7191,28 +7191,28 @@
         <v>220.948</v>
       </c>
       <c r="M72">
-        <v>97.29081600000001</v>
+        <v>98.68068480000001</v>
       </c>
       <c r="N72">
-        <v>123.657184</v>
+        <v>122.2673152</v>
       </c>
       <c r="O72">
-        <v>24.7314368</v>
+        <v>24.45346304</v>
       </c>
       <c r="P72">
-        <v>98.9257472</v>
+        <v>97.81385216</v>
       </c>
       <c r="Q72">
-        <v>99.10274720000001</v>
+        <v>97.99085216</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2550478971251109</v>
+        <v>0.2617599387329734</v>
       </c>
       <c r="T72">
-        <v>2.291350239195526</v>
+        <v>2.364849845905888</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.27100572370572</v>
+        <v>2.239019727597188</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1189647822325623</v>
+        <v>0.1189671953275912</v>
       </c>
       <c r="C73">
-        <v>672.6579281630866</v>
+        <v>654.2576255071365</v>
       </c>
       <c r="D73">
-        <v>1949.713928163086</v>
+        <v>1949.649625507136</v>
       </c>
       <c r="E73">
-        <v>173.0559999999998</v>
+        <v>191.3919999999998</v>
       </c>
       <c r="F73">
-        <v>1301.856</v>
+        <v>1320.192</v>
       </c>
       <c r="G73">
         <v>24.8</v>
@@ -7273,28 +7273,28 @@
         <v>220.948</v>
       </c>
       <c r="M73">
-        <v>98.68068479999999</v>
+        <v>100.0705536</v>
       </c>
       <c r="N73">
-        <v>122.2673152</v>
+        <v>120.8774464</v>
       </c>
       <c r="O73">
-        <v>24.45346304</v>
+        <v>24.17548928</v>
       </c>
       <c r="P73">
-        <v>97.81385216000001</v>
+        <v>96.70195712</v>
       </c>
       <c r="Q73">
-        <v>97.99085216000002</v>
+        <v>96.87895712000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2617599387329733</v>
+        <v>0.2689514118842544</v>
       </c>
       <c r="T73">
-        <v>2.364849845905887</v>
+        <v>2.443599424524132</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.239019727597189</v>
+        <v>2.207922231380561</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1189671953275912</v>
+        <v>0.1189696084226202</v>
       </c>
       <c r="C74">
-        <v>654.2576255071365</v>
+        <v>635.857327092521</v>
       </c>
       <c r="D74">
-        <v>1949.649625507136</v>
+        <v>1949.585327092521</v>
       </c>
       <c r="E74">
-        <v>191.3919999999998</v>
+        <v>209.7279999999998</v>
       </c>
       <c r="F74">
-        <v>1320.192</v>
+        <v>1338.528</v>
       </c>
       <c r="G74">
         <v>24.8</v>
@@ -7355,28 +7355,28 @@
         <v>220.948</v>
       </c>
       <c r="M74">
-        <v>100.0705536</v>
+        <v>101.4604224</v>
       </c>
       <c r="N74">
-        <v>120.8774464</v>
+        <v>119.4875776</v>
       </c>
       <c r="O74">
-        <v>24.17548928</v>
+        <v>23.89751552</v>
       </c>
       <c r="P74">
-        <v>96.70195712</v>
+        <v>95.59006208000001</v>
       </c>
       <c r="Q74">
-        <v>96.87895712000001</v>
+        <v>95.76706208000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2689514118842544</v>
+        <v>0.2766755867504453</v>
       </c>
       <c r="T74">
-        <v>2.443599424524132</v>
+        <v>2.528182305262246</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.207922231380561</v>
+        <v>2.177676721361649</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1189696084226202</v>
+        <v>0.1189720215176492</v>
       </c>
       <c r="C75">
-        <v>635.857327092521</v>
+        <v>617.4570329188214</v>
       </c>
       <c r="D75">
-        <v>1949.585327092521</v>
+        <v>1949.521032918821</v>
       </c>
       <c r="E75">
-        <v>209.7279999999998</v>
+        <v>228.0639999999999</v>
       </c>
       <c r="F75">
-        <v>1338.528</v>
+        <v>1356.864</v>
       </c>
       <c r="G75">
         <v>24.8</v>
@@ -7437,28 +7437,28 @@
         <v>220.948</v>
       </c>
       <c r="M75">
-        <v>101.4604224</v>
+        <v>102.8502912</v>
       </c>
       <c r="N75">
-        <v>119.4875776</v>
+        <v>118.0977088</v>
       </c>
       <c r="O75">
-        <v>23.89751552</v>
+        <v>23.61954176</v>
       </c>
       <c r="P75">
-        <v>95.59006208000001</v>
+        <v>94.47816704000002</v>
       </c>
       <c r="Q75">
-        <v>95.76706208000002</v>
+        <v>94.65516704000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2766755867504453</v>
+        <v>0.2849939289140355</v>
       </c>
       <c r="T75">
-        <v>2.528182305262246</v>
+        <v>2.619271561441754</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.177676721361649</v>
+        <v>2.148248657559465</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1189720215176492</v>
+        <v>0.1189744346126782</v>
       </c>
       <c r="C76">
-        <v>617.4570329188214</v>
+        <v>599.056742985618</v>
       </c>
       <c r="D76">
-        <v>1949.521032918821</v>
+        <v>1949.456742985618</v>
       </c>
       <c r="E76">
-        <v>228.0639999999999</v>
+        <v>246.3999999999999</v>
       </c>
       <c r="F76">
-        <v>1356.864</v>
+        <v>1375.2</v>
       </c>
       <c r="G76">
         <v>24.8</v>
@@ -7519,28 +7519,28 @@
         <v>220.948</v>
       </c>
       <c r="M76">
-        <v>102.8502912</v>
+        <v>104.24016</v>
       </c>
       <c r="N76">
-        <v>118.0977088</v>
+        <v>116.70784</v>
       </c>
       <c r="O76">
-        <v>23.61954176</v>
+        <v>23.34156800000001</v>
       </c>
       <c r="P76">
-        <v>94.47816704000002</v>
+        <v>93.36627200000001</v>
       </c>
       <c r="Q76">
-        <v>94.65516704000002</v>
+        <v>93.54327200000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2849939289140355</v>
+        <v>0.2939777384507129</v>
       </c>
       <c r="T76">
-        <v>2.619271561441754</v>
+        <v>2.717647958115624</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.148248657559465</v>
+        <v>2.119605342125339</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1189744346126782</v>
+        <v>0.1189768477077072</v>
       </c>
       <c r="C77">
-        <v>599.056742985618</v>
+        <v>580.6564572924906</v>
       </c>
       <c r="D77">
-        <v>1949.456742985618</v>
+        <v>1949.392457292491</v>
       </c>
       <c r="E77">
-        <v>246.3999999999999</v>
+        <v>264.7360000000001</v>
       </c>
       <c r="F77">
-        <v>1375.2</v>
+        <v>1393.536</v>
       </c>
       <c r="G77">
         <v>24.8</v>
@@ -7601,28 +7601,28 @@
         <v>220.948</v>
       </c>
       <c r="M77">
-        <v>104.24016</v>
+        <v>105.6300288</v>
       </c>
       <c r="N77">
-        <v>116.70784</v>
+        <v>115.3179712</v>
       </c>
       <c r="O77">
-        <v>23.34156800000001</v>
+        <v>23.06359424</v>
       </c>
       <c r="P77">
-        <v>93.36627200000001</v>
+        <v>92.25437695999999</v>
       </c>
       <c r="Q77">
-        <v>93.54327200000002</v>
+        <v>92.43137695999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2939777384507129</v>
+        <v>0.3037101987821134</v>
       </c>
       <c r="T77">
-        <v>2.717647958115624</v>
+        <v>2.824222387845648</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.119605342125339</v>
+        <v>2.091715798150005</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1189768477077072</v>
+        <v>0.1189792608027362</v>
       </c>
       <c r="C78">
-        <v>580.6564572924906</v>
+        <v>562.2561758390211</v>
       </c>
       <c r="D78">
-        <v>1949.392457292491</v>
+        <v>1949.328175839021</v>
       </c>
       <c r="E78">
-        <v>264.7360000000001</v>
+        <v>283.0720000000001</v>
       </c>
       <c r="F78">
-        <v>1393.536</v>
+        <v>1411.872</v>
       </c>
       <c r="G78">
         <v>24.8</v>
@@ -7683,28 +7683,28 @@
         <v>220.948</v>
       </c>
       <c r="M78">
-        <v>105.6300288</v>
+        <v>107.0198976</v>
       </c>
       <c r="N78">
-        <v>115.3179712</v>
+        <v>113.9281024</v>
       </c>
       <c r="O78">
-        <v>23.06359424</v>
+        <v>22.78562048</v>
       </c>
       <c r="P78">
-        <v>92.25437695999999</v>
+        <v>91.14248191999999</v>
       </c>
       <c r="Q78">
-        <v>92.43137695999999</v>
+        <v>91.31948192</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3037101987821134</v>
+        <v>0.3142889600118965</v>
       </c>
       <c r="T78">
-        <v>2.824222387845648</v>
+        <v>2.940064159291327</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.091715798150005</v>
+        <v>2.064550657914291</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1189792608027362</v>
+        <v>0.1189816738977652</v>
       </c>
       <c r="C79">
-        <v>562.2561758390211</v>
+        <v>543.8558986247888</v>
       </c>
       <c r="D79">
-        <v>1949.328175839021</v>
+        <v>1949.263898624789</v>
       </c>
       <c r="E79">
-        <v>283.0720000000001</v>
+        <v>301.4080000000001</v>
       </c>
       <c r="F79">
-        <v>1411.872</v>
+        <v>1430.208</v>
       </c>
       <c r="G79">
         <v>24.8</v>
@@ -7765,28 +7765,28 @@
         <v>220.948</v>
       </c>
       <c r="M79">
-        <v>107.0198976</v>
+        <v>108.4097664</v>
       </c>
       <c r="N79">
-        <v>113.9281024</v>
+        <v>112.5382336</v>
       </c>
       <c r="O79">
-        <v>22.78562048</v>
+        <v>22.50764672</v>
       </c>
       <c r="P79">
-        <v>91.14248191999999</v>
+        <v>90.03058688</v>
       </c>
       <c r="Q79">
-        <v>91.31948192</v>
+        <v>90.20758688000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3142889600118965</v>
+        <v>0.3258294268080237</v>
       </c>
       <c r="T79">
-        <v>2.940064159291327</v>
+        <v>3.066437000868431</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.064550657914291</v>
+        <v>2.038082059735902</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1189816738977652</v>
+        <v>0.1189840869927942</v>
       </c>
       <c r="C80">
-        <v>543.8558986247888</v>
+        <v>525.455625649375</v>
       </c>
       <c r="D80">
-        <v>1949.263898624789</v>
+        <v>1949.199625649375</v>
       </c>
       <c r="E80">
-        <v>301.4080000000001</v>
+        <v>319.7440000000001</v>
       </c>
       <c r="F80">
-        <v>1430.208</v>
+        <v>1448.544</v>
       </c>
       <c r="G80">
         <v>24.8</v>
@@ -7847,28 +7847,28 @@
         <v>220.948</v>
       </c>
       <c r="M80">
-        <v>108.4097664</v>
+        <v>109.7996352</v>
       </c>
       <c r="N80">
-        <v>112.5382336</v>
+        <v>111.1483648</v>
       </c>
       <c r="O80">
-        <v>22.50764672</v>
+        <v>22.22967296</v>
       </c>
       <c r="P80">
-        <v>90.03058688</v>
+        <v>88.91869183999999</v>
       </c>
       <c r="Q80">
-        <v>90.20758688000001</v>
+        <v>89.09569184</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3258294268080237</v>
+        <v>0.3384689856799724</v>
       </c>
       <c r="T80">
-        <v>3.066437000868431</v>
+        <v>3.204845351167164</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.038082059735902</v>
+        <v>2.012283552650637</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1189840869927942</v>
+        <v>0.1280745000878232</v>
       </c>
       <c r="C81">
-        <v>525.455625649375</v>
+        <v>291.7548433302525</v>
       </c>
       <c r="D81">
-        <v>1949.199625649375</v>
+        <v>1733.834843330253</v>
       </c>
       <c r="E81">
-        <v>319.7440000000001</v>
+        <v>338.0800000000002</v>
       </c>
       <c r="F81">
-        <v>1448.544</v>
+        <v>1466.88</v>
       </c>
       <c r="G81">
         <v>24.8</v>
@@ -7929,45 +7929,45 @@
         <v>220.948</v>
       </c>
       <c r="M81">
-        <v>109.7996352</v>
+        <v>132.0192</v>
       </c>
       <c r="N81">
-        <v>111.1483648</v>
+        <v>88.9288</v>
       </c>
       <c r="O81">
-        <v>22.22967296</v>
+        <v>17.78576</v>
       </c>
       <c r="P81">
-        <v>88.91869183999999</v>
+        <v>71.14304</v>
       </c>
       <c r="Q81">
-        <v>89.09569184</v>
+        <v>71.32004000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3384689856799724</v>
+        <v>0.352372500439116</v>
       </c>
       <c r="T81">
-        <v>3.204845351167164</v>
+        <v>3.357094536495771</v>
       </c>
       <c r="U81">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V81">
         <v>0.2</v>
       </c>
       <c r="W81">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>2.012283552650637</v>
+        <v>1.673605051386465</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1280745000878232</v>
+        <v>0.1281905131828522</v>
       </c>
       <c r="C82">
-        <v>291.7548433302525</v>
+        <v>270.9774512491344</v>
       </c>
       <c r="D82">
-        <v>1733.834843330253</v>
+        <v>1731.393451249135</v>
       </c>
       <c r="E82">
-        <v>338.0800000000002</v>
+        <v>356.4160000000002</v>
       </c>
       <c r="F82">
-        <v>1466.88</v>
+        <v>1485.216</v>
       </c>
       <c r="G82">
         <v>24.8</v>
@@ -8011,28 +8011,28 @@
         <v>220.948</v>
       </c>
       <c r="M82">
-        <v>132.0192</v>
+        <v>133.66944</v>
       </c>
       <c r="N82">
-        <v>88.9288</v>
+        <v>87.27856</v>
       </c>
       <c r="O82">
-        <v>17.78576</v>
+        <v>17.455712</v>
       </c>
       <c r="P82">
-        <v>71.14304</v>
+        <v>69.82284799999999</v>
       </c>
       <c r="Q82">
-        <v>71.32004000000001</v>
+        <v>69.999848</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.352372500439116</v>
+        <v>0.3677395430676432</v>
       </c>
       <c r="T82">
-        <v>3.357094536495771</v>
+        <v>3.525369951858968</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.673605051386465</v>
+        <v>1.652943260628607</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1281905131828522</v>
+        <v>0.1283065262778812</v>
       </c>
       <c r="C83">
-        <v>270.9774512491344</v>
+        <v>250.2069248903852</v>
       </c>
       <c r="D83">
-        <v>1731.393451249135</v>
+        <v>1728.958924890385</v>
       </c>
       <c r="E83">
-        <v>356.4160000000002</v>
+        <v>374.7520000000002</v>
       </c>
       <c r="F83">
-        <v>1485.216</v>
+        <v>1503.552</v>
       </c>
       <c r="G83">
         <v>24.8</v>
@@ -8093,28 +8093,28 @@
         <v>220.948</v>
       </c>
       <c r="M83">
-        <v>133.66944</v>
+        <v>135.31968</v>
       </c>
       <c r="N83">
-        <v>87.27856</v>
+        <v>85.62832</v>
       </c>
       <c r="O83">
-        <v>17.455712</v>
+        <v>17.125664</v>
       </c>
       <c r="P83">
-        <v>69.82284799999999</v>
+        <v>68.502656</v>
       </c>
       <c r="Q83">
-        <v>69.999848</v>
+        <v>68.67965600000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3677395430676432</v>
+        <v>0.3848140348771177</v>
       </c>
       <c r="T83">
-        <v>3.525369951858968</v>
+        <v>3.712342635595852</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.652943260628607</v>
+        <v>1.632785415986795</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1283065262778812</v>
+        <v>0.1284225393729101</v>
       </c>
       <c r="C84">
-        <v>250.2069248903852</v>
+        <v>229.4432353328275</v>
       </c>
       <c r="D84">
-        <v>1728.958924890385</v>
+        <v>1726.531235332828</v>
       </c>
       <c r="E84">
-        <v>374.7520000000002</v>
+        <v>393.0880000000002</v>
       </c>
       <c r="F84">
-        <v>1503.552</v>
+        <v>1521.888</v>
       </c>
       <c r="G84">
         <v>24.8</v>
@@ -8175,28 +8175,28 @@
         <v>220.948</v>
       </c>
       <c r="M84">
-        <v>135.31968</v>
+        <v>136.96992</v>
       </c>
       <c r="N84">
-        <v>85.62832</v>
+        <v>83.97808000000001</v>
       </c>
       <c r="O84">
-        <v>17.125664</v>
+        <v>16.795616</v>
       </c>
       <c r="P84">
-        <v>68.502656</v>
+        <v>67.18246400000001</v>
       </c>
       <c r="Q84">
-        <v>68.67965600000001</v>
+        <v>67.35946400000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3848140348771177</v>
+        <v>0.4038972904288834</v>
       </c>
       <c r="T84">
-        <v>3.712342635595852</v>
+        <v>3.921312105654724</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.632785415986795</v>
+        <v>1.613113302541171</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1284225393729101</v>
+        <v>0.1285385524679391</v>
       </c>
       <c r="C85">
-        <v>229.4432353328275</v>
+        <v>208.686353817493</v>
       </c>
       <c r="D85">
-        <v>1726.531235332828</v>
+        <v>1724.110353817493</v>
       </c>
       <c r="E85">
-        <v>393.0880000000002</v>
+        <v>411.4240000000002</v>
       </c>
       <c r="F85">
-        <v>1521.888</v>
+        <v>1540.224</v>
       </c>
       <c r="G85">
         <v>24.8</v>
@@ -8257,28 +8257,28 @@
         <v>220.948</v>
       </c>
       <c r="M85">
-        <v>136.96992</v>
+        <v>138.62016</v>
       </c>
       <c r="N85">
-        <v>83.97808000000001</v>
+        <v>82.32784000000001</v>
       </c>
       <c r="O85">
-        <v>16.795616</v>
+        <v>16.465568</v>
       </c>
       <c r="P85">
-        <v>67.18246400000001</v>
+        <v>65.862272</v>
       </c>
       <c r="Q85">
-        <v>67.35946400000002</v>
+        <v>66.03927200000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4038972904288834</v>
+        <v>0.4253659529246199</v>
       </c>
       <c r="T85">
-        <v>3.921312105654724</v>
+        <v>4.156402759470955</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.613113302541171</v>
+        <v>1.593909572749014</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1285385524679392</v>
+        <v>0.1286545655629681</v>
       </c>
       <c r="C86">
-        <v>208.6863538174925</v>
+        <v>187.9362517464863</v>
       </c>
       <c r="D86">
-        <v>1724.110353817493</v>
+        <v>1721.696251746486</v>
       </c>
       <c r="E86">
-        <v>411.424</v>
+        <v>429.76</v>
       </c>
       <c r="F86">
-        <v>1540.224</v>
+        <v>1558.56</v>
       </c>
       <c r="G86">
         <v>24.8</v>
@@ -8339,28 +8339,28 @@
         <v>220.948</v>
       </c>
       <c r="M86">
-        <v>138.62016</v>
+        <v>140.2704</v>
       </c>
       <c r="N86">
-        <v>82.32784000000001</v>
+        <v>80.67760000000001</v>
       </c>
       <c r="O86">
-        <v>16.465568</v>
+        <v>16.13552</v>
       </c>
       <c r="P86">
-        <v>65.862272</v>
+        <v>64.54208000000001</v>
       </c>
       <c r="Q86">
-        <v>66.03927200000001</v>
+        <v>64.71908000000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4253659529246197</v>
+        <v>0.4496971037531209</v>
       </c>
       <c r="T86">
-        <v>4.156402759470953</v>
+        <v>4.422838833796014</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.593909572749014</v>
+        <v>1.575157695422555</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1286545655629681</v>
+        <v>0.1287705786579971</v>
       </c>
       <c r="C87">
-        <v>187.9362517464863</v>
+        <v>167.1929006818609</v>
       </c>
       <c r="D87">
-        <v>1721.696251746486</v>
+        <v>1719.288900681861</v>
       </c>
       <c r="E87">
-        <v>429.76</v>
+        <v>448.096</v>
       </c>
       <c r="F87">
-        <v>1558.56</v>
+        <v>1576.896</v>
       </c>
       <c r="G87">
         <v>24.8</v>
@@ -8421,28 +8421,28 @@
         <v>220.948</v>
       </c>
       <c r="M87">
-        <v>140.2704</v>
+        <v>141.92064</v>
       </c>
       <c r="N87">
-        <v>80.67760000000001</v>
+        <v>79.02736000000002</v>
       </c>
       <c r="O87">
-        <v>16.13552</v>
+        <v>15.805472</v>
       </c>
       <c r="P87">
-        <v>64.54208000000001</v>
+        <v>63.22188800000001</v>
       </c>
       <c r="Q87">
-        <v>64.71908000000002</v>
+        <v>63.39888800000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4496971037531209</v>
+        <v>0.4775041332714081</v>
       </c>
       <c r="T87">
-        <v>4.422838833796014</v>
+        <v>4.727337204453227</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.575157695422555</v>
+        <v>1.556841908266479</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1287705786579971</v>
+        <v>0.1288865917530261</v>
       </c>
       <c r="C88">
-        <v>167.1929006818609</v>
+        <v>146.4562723444992</v>
       </c>
       <c r="D88">
-        <v>1719.288900681861</v>
+        <v>1716.888272344499</v>
       </c>
       <c r="E88">
-        <v>448.096</v>
+        <v>466.432</v>
       </c>
       <c r="F88">
-        <v>1576.896</v>
+        <v>1595.232</v>
       </c>
       <c r="G88">
         <v>24.8</v>
@@ -8503,28 +8503,28 @@
         <v>220.948</v>
       </c>
       <c r="M88">
-        <v>141.92064</v>
+        <v>143.57088</v>
       </c>
       <c r="N88">
-        <v>79.02736000000002</v>
+        <v>77.37712000000002</v>
       </c>
       <c r="O88">
-        <v>15.805472</v>
+        <v>15.475424</v>
       </c>
       <c r="P88">
-        <v>63.22188800000001</v>
+        <v>61.90169600000002</v>
       </c>
       <c r="Q88">
-        <v>63.39888800000001</v>
+        <v>62.07869600000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4775041332714081</v>
+        <v>0.5095891673309701</v>
       </c>
       <c r="T88">
-        <v>4.727337204453227</v>
+        <v>5.078681478288472</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.556841908266479</v>
+        <v>1.538947173688704</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1288865917530261</v>
+        <v>0.1290026048480551</v>
       </c>
       <c r="C89">
-        <v>146.4562723444992</v>
+        <v>125.7263386130089</v>
       </c>
       <c r="D89">
-        <v>1716.888272344499</v>
+        <v>1714.494338613009</v>
       </c>
       <c r="E89">
-        <v>466.432</v>
+        <v>484.768</v>
       </c>
       <c r="F89">
-        <v>1595.232</v>
+        <v>1613.568</v>
       </c>
       <c r="G89">
         <v>24.8</v>
@@ -8585,28 +8585,28 @@
         <v>220.948</v>
       </c>
       <c r="M89">
-        <v>143.57088</v>
+        <v>145.22112</v>
       </c>
       <c r="N89">
-        <v>77.37712000000002</v>
+        <v>75.72688000000002</v>
       </c>
       <c r="O89">
-        <v>15.475424</v>
+        <v>15.14537600000001</v>
       </c>
       <c r="P89">
-        <v>61.90169600000002</v>
+        <v>60.58150400000002</v>
       </c>
       <c r="Q89">
-        <v>62.07869600000001</v>
+        <v>60.75850400000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5095891673309701</v>
+        <v>0.5470217070671259</v>
       </c>
       <c r="T89">
-        <v>5.078681478288472</v>
+        <v>5.488583131096259</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.538947173688704</v>
+        <v>1.521459137624059</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1290026048480551</v>
+        <v>0.1291186179430841</v>
       </c>
       <c r="C90">
-        <v>125.7263386130089</v>
+        <v>105.0030715226203</v>
       </c>
       <c r="D90">
-        <v>1714.494338613009</v>
+        <v>1712.10707152262</v>
       </c>
       <c r="E90">
-        <v>484.768</v>
+        <v>503.104</v>
       </c>
       <c r="F90">
-        <v>1613.568</v>
+        <v>1631.904</v>
       </c>
       <c r="G90">
         <v>24.8</v>
@@ -8667,28 +8667,28 @@
         <v>220.948</v>
       </c>
       <c r="M90">
-        <v>145.22112</v>
+        <v>146.87136</v>
       </c>
       <c r="N90">
-        <v>75.72688000000002</v>
+        <v>74.07664000000003</v>
       </c>
       <c r="O90">
-        <v>15.14537600000001</v>
+        <v>14.81532800000001</v>
       </c>
       <c r="P90">
-        <v>60.58150400000002</v>
+        <v>59.26131200000002</v>
       </c>
       <c r="Q90">
-        <v>60.75850400000002</v>
+        <v>59.43831200000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5470217070671259</v>
+        <v>0.5912601631189465</v>
       </c>
       <c r="T90">
-        <v>5.488583131096259</v>
+        <v>5.973012357141825</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.521459137624059</v>
+        <v>1.504364091133901</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1291186179430841</v>
+        <v>0.1736103256073273</v>
       </c>
       <c r="C91">
-        <v>105.0030715226203</v>
+        <v>-509.3299025411163</v>
       </c>
       <c r="D91">
-        <v>1712.10707152262</v>
+        <v>1116.110097458884</v>
       </c>
       <c r="E91">
-        <v>503.104</v>
+        <v>521.4400000000001</v>
       </c>
       <c r="F91">
-        <v>1631.904</v>
+        <v>1650.24</v>
       </c>
       <c r="G91">
         <v>24.8</v>
@@ -8749,45 +8749,45 @@
         <v>220.948</v>
       </c>
       <c r="M91">
-        <v>146.87136</v>
+        <v>242.255232</v>
       </c>
       <c r="N91">
-        <v>74.07664000000003</v>
+        <v>-21.30723200000003</v>
       </c>
       <c r="O91">
-        <v>14.81532800000001</v>
+        <v>-4.261446400000006</v>
       </c>
       <c r="P91">
-        <v>59.26131200000002</v>
+        <v>-17.04578560000002</v>
       </c>
       <c r="Q91">
-        <v>59.43831200000002</v>
+        <v>-16.86878560000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5912601631189465</v>
+        <v>0.6559023834729242</v>
       </c>
       <c r="T91">
-        <v>5.973012357141825</v>
+        <v>6.680871165307797</v>
       </c>
       <c r="U91">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2</v>
+        <v>0.1824092699058817</v>
       </c>
       <c r="W91">
-        <v>0.07199999999999999</v>
+        <v>0.1200223191778166</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.504364091133901</v>
+        <v>0.9120463495294087</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1736103256073273</v>
+        <v>0.1746203256073273</v>
       </c>
       <c r="C92">
-        <v>-509.3299025411163</v>
+        <v>-536.416627188946</v>
       </c>
       <c r="D92">
-        <v>1116.110097458884</v>
+        <v>1107.359372811054</v>
       </c>
       <c r="E92">
-        <v>521.4400000000001</v>
+        <v>539.7760000000001</v>
       </c>
       <c r="F92">
-        <v>1650.24</v>
+        <v>1668.576</v>
       </c>
       <c r="G92">
         <v>24.8</v>
@@ -8831,37 +8831,37 @@
         <v>220.948</v>
       </c>
       <c r="M92">
-        <v>242.255232</v>
+        <v>244.9469568</v>
       </c>
       <c r="N92">
-        <v>-21.30723200000003</v>
+        <v>-23.99895680000003</v>
       </c>
       <c r="O92">
-        <v>-4.261446400000006</v>
+        <v>-4.799791360000007</v>
       </c>
       <c r="P92">
-        <v>-17.04578560000002</v>
+        <v>-19.19916544000002</v>
       </c>
       <c r="Q92">
-        <v>-16.86878560000002</v>
+        <v>-19.02216544000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6559023834729242</v>
+        <v>0.7236915371921382</v>
       </c>
       <c r="T92">
-        <v>6.680871165307797</v>
+        <v>7.423190183675331</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1824092699058817</v>
+        <v>0.1804047724343885</v>
       </c>
       <c r="W92">
-        <v>0.1200223191778166</v>
+        <v>0.1203165794066318</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9120463495294087</v>
+        <v>0.9020238621719425</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1746203256073273</v>
+        <v>0.1756303256073273</v>
       </c>
       <c r="C93">
-        <v>-536.416627188946</v>
+        <v>-563.3672013364519</v>
       </c>
       <c r="D93">
-        <v>1107.359372811054</v>
+        <v>1098.744798663548</v>
       </c>
       <c r="E93">
-        <v>539.7760000000001</v>
+        <v>558.1120000000001</v>
       </c>
       <c r="F93">
-        <v>1668.576</v>
+        <v>1686.912</v>
       </c>
       <c r="G93">
         <v>24.8</v>
@@ -8913,37 +8913,37 @@
         <v>220.948</v>
       </c>
       <c r="M93">
-        <v>244.9469568</v>
+        <v>247.6386816</v>
       </c>
       <c r="N93">
-        <v>-23.99895680000003</v>
+        <v>-26.69068160000003</v>
       </c>
       <c r="O93">
-        <v>-4.799791360000007</v>
+        <v>-5.338136320000007</v>
       </c>
       <c r="P93">
-        <v>-19.19916544000002</v>
+        <v>-21.35254528000003</v>
       </c>
       <c r="Q93">
-        <v>-19.02216544000002</v>
+        <v>-21.17554528000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7236915371921382</v>
+        <v>0.8084279793411556</v>
       </c>
       <c r="T93">
-        <v>7.423190183675331</v>
+        <v>8.351088956634749</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1804047724343885</v>
+        <v>0.1784438509948843</v>
       </c>
       <c r="W93">
-        <v>0.1203165794066318</v>
+        <v>0.120604442673951</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9020238621719425</v>
+        <v>0.8922192549744214</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1756303256073273</v>
+        <v>0.1766403256073273</v>
       </c>
       <c r="C94">
-        <v>-563.3672013364519</v>
+        <v>-590.1847779566497</v>
       </c>
       <c r="D94">
-        <v>1098.744798663548</v>
+        <v>1090.26322204335</v>
       </c>
       <c r="E94">
-        <v>558.1120000000001</v>
+        <v>576.4480000000001</v>
       </c>
       <c r="F94">
-        <v>1686.912</v>
+        <v>1705.248</v>
       </c>
       <c r="G94">
         <v>24.8</v>
@@ -8995,37 +8995,37 @@
         <v>220.948</v>
       </c>
       <c r="M94">
-        <v>247.6386816</v>
+        <v>250.3304064</v>
       </c>
       <c r="N94">
-        <v>-26.69068160000003</v>
+        <v>-29.38240640000004</v>
       </c>
       <c r="O94">
-        <v>-5.338136320000007</v>
+        <v>-5.876481280000007</v>
       </c>
       <c r="P94">
-        <v>-21.35254528000003</v>
+        <v>-23.50592512000003</v>
       </c>
       <c r="Q94">
-        <v>-21.17554528000003</v>
+        <v>-23.32892512000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8084279793411556</v>
+        <v>0.9173748335327492</v>
       </c>
       <c r="T94">
-        <v>8.351088956634749</v>
+        <v>9.544101664725426</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1784438509948843</v>
+        <v>0.1765250999089178</v>
       </c>
       <c r="W94">
-        <v>0.120604442673951</v>
+        <v>0.1208861153333709</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8922192549744214</v>
+        <v>0.882625499544589</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1766403256073273</v>
+        <v>0.1776503256073273</v>
       </c>
       <c r="C95">
-        <v>-590.1847779566497</v>
+        <v>-616.8724134129266</v>
       </c>
       <c r="D95">
-        <v>1090.26322204335</v>
+        <v>1081.911586587074</v>
       </c>
       <c r="E95">
-        <v>576.4480000000001</v>
+        <v>594.7840000000001</v>
       </c>
       <c r="F95">
-        <v>1705.248</v>
+        <v>1723.584</v>
       </c>
       <c r="G95">
         <v>24.8</v>
@@ -9077,37 +9077,37 @@
         <v>220.948</v>
       </c>
       <c r="M95">
-        <v>250.3304064</v>
+        <v>253.0221312</v>
       </c>
       <c r="N95">
-        <v>-29.38240640000004</v>
+        <v>-32.07413120000004</v>
       </c>
       <c r="O95">
-        <v>-5.876481280000007</v>
+        <v>-6.414826240000008</v>
       </c>
       <c r="P95">
-        <v>-23.50592512000003</v>
+        <v>-25.65930496000003</v>
       </c>
       <c r="Q95">
-        <v>-23.32892512000003</v>
+        <v>-25.48230496000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9173748335327492</v>
+        <v>1.062637305788208</v>
       </c>
       <c r="T95">
-        <v>9.544101664725426</v>
+        <v>11.134785275513</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1765250999089178</v>
+        <v>0.1746471733141421</v>
       </c>
       <c r="W95">
-        <v>0.1208861153333709</v>
+        <v>0.1211617949574839</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.882625499544589</v>
+        <v>0.8732358665707103</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1776503256073273</v>
+        <v>0.1786603256073274</v>
       </c>
       <c r="C96">
-        <v>-616.8724134129266</v>
+        <v>-643.4330711311575</v>
       </c>
       <c r="D96">
-        <v>1081.911586587074</v>
+        <v>1073.686928868843</v>
       </c>
       <c r="E96">
-        <v>594.7840000000001</v>
+        <v>613.1200000000001</v>
       </c>
       <c r="F96">
-        <v>1723.584</v>
+        <v>1741.92</v>
       </c>
       <c r="G96">
         <v>24.8</v>
@@ -9159,37 +9159,37 @@
         <v>220.948</v>
       </c>
       <c r="M96">
-        <v>253.0221312</v>
+        <v>255.713856</v>
       </c>
       <c r="N96">
-        <v>-32.07413120000004</v>
+        <v>-34.76585600000001</v>
       </c>
       <c r="O96">
-        <v>-6.414826240000008</v>
+        <v>-6.953171200000003</v>
       </c>
       <c r="P96">
-        <v>-25.65930496000003</v>
+        <v>-27.81268480000001</v>
       </c>
       <c r="Q96">
-        <v>-25.48230496000003</v>
+        <v>-27.63568480000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.062637305788208</v>
+        <v>1.26600476694585</v>
       </c>
       <c r="T96">
-        <v>11.134785275513</v>
+        <v>13.36174233061561</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1746471733141421</v>
+        <v>0.1728087820160985</v>
       </c>
       <c r="W96">
-        <v>0.1211617949574839</v>
+        <v>0.1214316708000368</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8732358665707103</v>
+        <v>0.8640439100804924</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1786603256073274</v>
+        <v>0.1796703256073273</v>
       </c>
       <c r="C97">
-        <v>-643.4330711311575</v>
+        <v>-669.8696251055937</v>
       </c>
       <c r="D97">
-        <v>1073.686928868843</v>
+        <v>1065.586374894406</v>
       </c>
       <c r="E97">
-        <v>613.1200000000001</v>
+        <v>631.4560000000001</v>
       </c>
       <c r="F97">
-        <v>1741.92</v>
+        <v>1760.256</v>
       </c>
       <c r="G97">
         <v>24.8</v>
@@ -9241,37 +9241,37 @@
         <v>220.948</v>
       </c>
       <c r="M97">
-        <v>255.713856</v>
+        <v>258.4055808000001</v>
       </c>
       <c r="N97">
-        <v>-34.76585600000001</v>
+        <v>-37.45758080000004</v>
       </c>
       <c r="O97">
-        <v>-6.953171200000003</v>
+        <v>-7.49151616000001</v>
       </c>
       <c r="P97">
-        <v>-27.81268480000001</v>
+        <v>-29.96606464000003</v>
       </c>
       <c r="Q97">
-        <v>-27.63568480000001</v>
+        <v>-29.78906464000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.26600476694585</v>
+        <v>1.571055958682313</v>
       </c>
       <c r="T97">
-        <v>13.36174233061561</v>
+        <v>16.70217791326952</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1728087820160985</v>
+        <v>0.1710086905367641</v>
       </c>
       <c r="W97">
-        <v>0.1214316708000368</v>
+        <v>0.121695924229203</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8640439100804924</v>
+        <v>0.8550434526838205</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1796703256073273</v>
+        <v>0.1806803256073273</v>
       </c>
       <c r="C98">
-        <v>-669.8696251055935</v>
+        <v>-696.1848632472377</v>
       </c>
       <c r="D98">
-        <v>1065.586374894406</v>
+        <v>1057.607136752762</v>
       </c>
       <c r="E98">
-        <v>631.4559999999999</v>
+        <v>649.7919999999999</v>
       </c>
       <c r="F98">
-        <v>1760.256</v>
+        <v>1778.592</v>
       </c>
       <c r="G98">
         <v>24.8</v>
@@ -9323,37 +9323,37 @@
         <v>220.948</v>
       </c>
       <c r="M98">
-        <v>258.4055808</v>
+        <v>261.0973056</v>
       </c>
       <c r="N98">
-        <v>-37.45758079999999</v>
+        <v>-40.14930560000002</v>
       </c>
       <c r="O98">
-        <v>-7.491516159999998</v>
+        <v>-8.029861120000005</v>
       </c>
       <c r="P98">
-        <v>-29.96606463999999</v>
+        <v>-32.11944448000001</v>
       </c>
       <c r="Q98">
-        <v>-29.78906463999999</v>
+        <v>-31.94244448000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.571055958682309</v>
+        <v>2.079474611576412</v>
       </c>
       <c r="T98">
-        <v>16.70217791326947</v>
+        <v>22.26957055102596</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1710086905367642</v>
+        <v>0.1692457143456635</v>
       </c>
       <c r="W98">
-        <v>0.121695924229203</v>
+        <v>0.1219547291340566</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8550434526838206</v>
+        <v>0.8462285717283173</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1806803256073273</v>
+        <v>0.1816903256073273</v>
       </c>
       <c r="C99">
-        <v>-696.1848632472377</v>
+        <v>-722.3814905828942</v>
       </c>
       <c r="D99">
-        <v>1057.607136752762</v>
+        <v>1049.746509417106</v>
       </c>
       <c r="E99">
-        <v>649.7919999999999</v>
+        <v>668.1279999999999</v>
       </c>
       <c r="F99">
-        <v>1778.592</v>
+        <v>1796.928</v>
       </c>
       <c r="G99">
         <v>24.8</v>
@@ -9405,37 +9405,37 @@
         <v>220.948</v>
       </c>
       <c r="M99">
-        <v>261.0973056</v>
+        <v>263.7890304</v>
       </c>
       <c r="N99">
-        <v>-40.14930560000002</v>
+        <v>-42.84103039999999</v>
       </c>
       <c r="O99">
-        <v>-8.029861120000005</v>
+        <v>-8.56820608</v>
       </c>
       <c r="P99">
-        <v>-32.11944448000001</v>
+        <v>-34.27282432</v>
       </c>
       <c r="Q99">
-        <v>-31.94244448000001</v>
+        <v>-34.09582432</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.079474611576412</v>
+        <v>3.096311917364617</v>
       </c>
       <c r="T99">
-        <v>22.26957055102596</v>
+        <v>33.40435582653894</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1692457143456635</v>
+        <v>0.1675187172605037</v>
       </c>
       <c r="W99">
-        <v>0.1219547291340566</v>
+        <v>0.1222082523061581</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8462285717283173</v>
+        <v>0.8375935863025182</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1816903256073273</v>
+        <v>0.1827003256073273</v>
       </c>
       <c r="C100">
-        <v>-722.3814905828942</v>
+        <v>-748.462132312618</v>
       </c>
       <c r="D100">
-        <v>1049.746509417106</v>
+        <v>1042.001867687382</v>
       </c>
       <c r="E100">
-        <v>668.1279999999999</v>
+        <v>686.4639999999999</v>
       </c>
       <c r="F100">
-        <v>1796.928</v>
+        <v>1815.264</v>
       </c>
       <c r="G100">
         <v>24.8</v>
@@ -9487,37 +9487,37 @@
         <v>220.948</v>
       </c>
       <c r="M100">
-        <v>263.7890304</v>
+        <v>266.4807552</v>
       </c>
       <c r="N100">
-        <v>-42.84103039999999</v>
+        <v>-45.53275520000003</v>
       </c>
       <c r="O100">
-        <v>-8.56820608</v>
+        <v>-9.106551040000005</v>
       </c>
       <c r="P100">
-        <v>-34.27282432</v>
+        <v>-36.42620416000002</v>
       </c>
       <c r="Q100">
-        <v>-34.09582432</v>
+        <v>-36.24920416000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.096311917364617</v>
+        <v>6.146823834729235</v>
       </c>
       <c r="T100">
-        <v>33.40435582653894</v>
+        <v>66.80871165307789</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1675187172605037</v>
+        <v>0.165826609005347</v>
       </c>
       <c r="W100">
-        <v>0.1222082523061581</v>
+        <v>0.1224566537980151</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8375935863025182</v>
+        <v>0.8291330450267351</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1827003256073273</v>
-      </c>
-      <c r="C101">
-        <v>-748.462132312618</v>
-      </c>
-      <c r="D101">
-        <v>1042.001867687382</v>
-      </c>
-      <c r="E101">
-        <v>686.4639999999999</v>
-      </c>
-      <c r="F101">
-        <v>1815.264</v>
-      </c>
-      <c r="G101">
-        <v>24.8</v>
-      </c>
-      <c r="H101">
-        <v>704.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>221.125</v>
-      </c>
-      <c r="K101">
-        <v>0.177</v>
-      </c>
-      <c r="L101">
-        <v>220.948</v>
-      </c>
-      <c r="M101">
-        <v>266.4807552</v>
-      </c>
-      <c r="N101">
-        <v>-45.53275520000003</v>
-      </c>
-      <c r="O101">
-        <v>-9.106551040000005</v>
-      </c>
-      <c r="P101">
-        <v>-36.42620416000002</v>
-      </c>
-      <c r="Q101">
-        <v>-36.24920416000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.146823834729235</v>
-      </c>
-      <c r="T101">
-        <v>66.80871165307789</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.165826609005347</v>
-      </c>
-      <c r="W101">
-        <v>0.1224566537980151</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8291330450267351</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
